--- a/workspaces/btc_daily_14days/ma/ma_ratio_21.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_21.xlsx
@@ -575,46 +575,46 @@
         <v>34</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.388914620966496</v>
+        <v>3.377149461245232</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.106002482368837</v>
+        <v>-4.093125342841645</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.383231219058494</v>
+        <v>1.37829825432371</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.42935578415188</v>
+        <v>-1.425435211316</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.968648478775329</v>
+        <v>-1.962875740610102</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-16.39547237016905</v>
+        <v>-16.34305714159767</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-16.48440914088263</v>
+        <v>-16.43162316795478</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-16.95657370042373</v>
+        <v>-16.9020778536425</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-19.96903644202789</v>
+        <v>-19.90463720074251</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-17.87829002988786</v>
+        <v>-17.82060588713586</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-12.19116924386894</v>
+        <v>-12.15163103529977</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-12.15953959485259</v>
+        <v>-12.12034162267535</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-9.6343335240595</v>
+        <v>-9.603043278309379</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.5342809457650972</v>
+        <v>-0.5321994762467952</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>38</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.493438320208774</v>
+        <v>-2.486368237903541</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.473785702562239</v>
+        <v>-1.469200384727522</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.662412617428373</v>
+        <v>8.633822235101903</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.794985865195748</v>
+        <v>8.76587177795799</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.3556166744545735</v>
+        <v>0.353967293106308</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.6532611875296297</v>
+        <v>0.6514149865149079</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.56850154670488</v>
+        <v>0.5670192135588863</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.535672794916188</v>
+        <v>-2.526892517450683</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.597672893490497</v>
+        <v>-2.588364805572063</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.824602432931734</v>
+        <v>1.819525842496354</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.619773495554632</v>
+        <v>1.615302861137657</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.654802917335914</v>
+        <v>1.64997493716956</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.512479191396714</v>
+        <v>6.492049470119916</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.404984400929166</v>
+        <v>9.374921266785933</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>45</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.062117235344573</v>
+        <v>3.051143134934229</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.56483081800284</v>
+        <v>12.52354171936644</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.17304508683213</v>
+        <v>12.13236119724276</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.634843576686016</v>
+        <v>5.61546888000386</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.097246851094638</v>
+        <v>5.080036237771459</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.846140516345841</v>
+        <v>9.814153089650247</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9.763699424380697</v>
+        <v>9.732075880637929</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>9.297959204206784</v>
+        <v>9.268173120725727</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.238924934599531</v>
+        <v>9.209667984618157</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.389265621514042</v>
+        <v>8.362586517613053</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.18609284255102</v>
+        <v>8.160026940079817</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>14.90798425623902</v>
+        <v>14.85965701165061</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>14.49020385961108</v>
+        <v>14.44322348656024</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>16.97425861047093</v>
+        <v>16.91878091590873</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-11.22359705036871</v>
+        <v>-11.36533839959147</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.312160989151629</v>
+        <v>-3.352811411388501</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.88415635761573</v>
+        <v>-6.968606636251494</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.578456493024689</v>
+        <v>-3.620466091100752</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6483940397902046</v>
+        <v>0.6596665703803879</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.9462019770350452</v>
+        <v>0.9589402096244086</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.451285870090516</v>
+        <v>2.483212861121366</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.983710637030633</v>
+        <v>2.008231768021041</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.513413310130233</v>
+        <v>3.556475071336919</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.071331601189172</v>
+        <v>1.083322512117967</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.907799386622308</v>
+        <v>-3.960398071481009</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.9014257636020488</v>
+        <v>0.9133818195965588</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.25669352138425</v>
+        <v>5.325326732784532</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.03453241179764177</v>
+        <v>0.03706048580046684</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>91</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.748319921548273</v>
+        <v>5.72976706652863</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.8402990540759632</v>
+        <v>0.8372265477269636</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6539189248014878</v>
+        <v>-0.6527661376934262</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.875410838717983</v>
+        <v>3.862290422226721</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.937776421947746</v>
+        <v>9.905795494892516</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>10.23803666732944</v>
+        <v>10.20568798728688</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.753333177569935</v>
+        <v>5.735106697968227</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.387529616400712</v>
+        <v>6.367657653235874</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.2266803247187</v>
+        <v>5.210714816846938</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.131580449919589</v>
+        <v>-1.127598552331833</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.540955356356129</v>
+        <v>-3.529188387347283</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-9.017171036843457</v>
+        <v>-8.988917417751217</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.236150616066666</v>
+        <v>-7.213724299151437</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-8.08782506347255</v>
+        <v>-8.062904065776749</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>82</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.165098265155606</v>
+        <v>1.160414991271374</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.666390952985701</v>
+        <v>-1.661550032316221</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.818851578756004</v>
+        <v>2.808897291982795</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5091487989511094</v>
+        <v>0.5062386964454504</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.412116893386049</v>
+        <v>2.402839558715428</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.616394465365623</v>
+        <v>-4.60250403133594</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.404768422230319</v>
+        <v>1.399672525405251</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.2848545601468402</v>
+        <v>-0.2842040914704711</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.764374770019934</v>
+        <v>5.745941569003342</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.468488795731986</v>
+        <v>2.461085593516323</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.709041600231309</v>
+        <v>4.694840631949219</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.075687524708819</v>
+        <v>1.072814623545291</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.239082998659228</v>
+        <v>-4.225249359456988</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.764985371881664</v>
+        <v>-2.756015832058743</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.538819744306515</v>
+        <v>1.564115496985764</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.686088981113265</v>
+        <v>-1.707258506997078</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.373702234491212</v>
+        <v>4.43779441200526</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.312552636956134</v>
+        <v>5.39033821045269</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.197296520678861</v>
+        <v>7.302327002660448</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.651405989827765</v>
+        <v>2.690111865478308</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1439670046118096</v>
+        <v>0.1488509080666205</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.3242917865500345</v>
+        <v>-0.3276358487335074</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.001937955202145</v>
+        <v>-2.027797901878202</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.855245746248414</v>
+        <v>-2.895565684263055</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.296378784942775</v>
+        <v>-6.384493049918234</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.80566225232792</v>
+        <v>-5.886692287063148</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-7.381546952337544</v>
+        <v>-7.483945880848061</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-7.136144606847722</v>
+        <v>-7.234224548571774</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>146</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.616150720885756</v>
+        <v>1.610364560714913</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.115375386784137</v>
+        <v>4.103283009120958</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9804312193186036</v>
+        <v>0.9761321978442155</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.316308100656251</v>
+        <v>-2.311391053852923</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.227070208626749</v>
+        <v>-4.217187725525307</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1846091479457499</v>
+        <v>0.1832183789050035</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.016971737154861</v>
+        <v>-4.006033833468656</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.054926101372118</v>
+        <v>-1.052081470094379</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.23554128732156</v>
+        <v>-5.220519411614625</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.150180808073095</v>
+        <v>-8.126028235027405</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.55012594564991</v>
+        <v>-3.538676268704158</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.576245071409573</v>
+        <v>-5.559087631906827</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.684781373711793</v>
+        <v>-6.664273749701202</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.80792400962256</v>
+        <v>-7.784415431123229</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.004853845324234</v>
+        <v>-5.013016047934421</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.050772358514998</v>
+        <v>-2.054015482653675</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.64455983488547</v>
+        <v>-5.653696062024949</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-8.258040208691838</v>
+        <v>-8.271937644929885</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.313146272464671</v>
+        <v>-3.317925330208347</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1846874860168128</v>
+        <v>0.1855918186600292</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.187843846335568</v>
+        <v>-2.191660849350761</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.114387195402358</v>
+        <v>-3.119945555028622</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.719274067275492</v>
+        <v>-2.724508721161477</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.657941068406075</v>
+        <v>-2.663752398541938</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.771375623009547</v>
+        <v>-0.7738151401380122</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.279101501567439</v>
+        <v>-0.2807163864624158</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.2405283050791596</v>
+        <v>-0.2422554010769318</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.82289129771047</v>
+        <v>-1.827396454121853</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.232934118529208</v>
+        <v>-1.234584228706339</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-7.889105404729321</v>
+        <v>-7.90111677926042</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-11.22988647150595</v>
+        <v>-11.24691259383437</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-10.26219834460016</v>
+        <v>-10.27804973640738</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-8.700495937192038</v>
+        <v>-8.713218378896393</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-9.857456884311205</v>
+        <v>-9.872169725407637</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.156247413751892</v>
+        <v>-6.165891128498771</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.729281357006798</v>
+        <v>-8.743070906436827</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.265864059287502</v>
+        <v>-6.276155475471164</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.852403045989128</v>
+        <v>-5.862678507648724</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-7.320879774086485</v>
+        <v>-7.333254616776522</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.601388815107349</v>
+        <v>-5.611107746350733</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.020831600908863</v>
+        <v>-6.031362357295926</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.771396795153663</v>
+        <v>-5.781641025019447</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.065765364235133</v>
+        <v>-4.096224877954064</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.365049416608059</v>
+        <v>-5.40978900035514</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8461835101389212</v>
+        <v>0.8477482733967605</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.92094223396942</v>
+        <v>1.929588960649355</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.9625254960958785</v>
+        <v>-0.971187126614339</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.6652188406912813</v>
+        <v>-0.6733722367118418</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.519913982586552</v>
+        <v>-1.535878182553972</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4094313384408323</v>
+        <v>-0.4193329503902561</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1595675659920346</v>
+        <v>0.1538307105985126</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.5042043758882926</v>
+        <v>-0.5180934162283606</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.812970324173264</v>
+        <v>1.816835799136605</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6743215036640109</v>
+        <v>-0.6884635832005088</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1699304463313922</v>
+        <v>0.161123075695869</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.787225022121511</v>
+        <v>-1.811377814250072</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.977974402684204</v>
+        <v>-2.001587745866985</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.01819548235584278</v>
+        <v>0.00662621166706856</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.812924943761551</v>
+        <v>-2.847150674506011</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4782337136900239</v>
+        <v>-0.4895549085035995</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.015775908338824</v>
+        <v>-1.028945656958768</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4608415626562632</v>
+        <v>-0.4706992392232792</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.348725352035707</v>
+        <v>-2.380288689928044</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.699110319971084</v>
+        <v>-3.746380976923646</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.872836145264621</v>
+        <v>-3.92144045342252</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.420122688234287</v>
+        <v>-3.469482305117175</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.141300183277124</v>
+        <v>-4.195068962768026</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.10581281825251</v>
+        <v>-4.160685805422652</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.458530400163987</v>
+        <v>-2.497607083034161</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.950596982525099</v>
+        <v>-1.987469084091266</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5.902529229300946</v>
+        <v>-5.921589836149494</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.231494146612974</v>
+        <v>-4.24746207562437</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.762108900640349</v>
+        <v>-5.781931921822107</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.621850827321396</v>
+        <v>-7.645980783516599</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.171018089824351</v>
+        <v>-6.190100004286641</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.885310341832088</v>
+        <v>-3.898356072269117</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.820216984005512</v>
+        <v>-4.83779064424219</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.011955718755509</v>
+        <v>-3.025771763821538</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.925104814423932</v>
+        <v>-3.941472504704635</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.78264106664556</v>
+        <v>-2.79729569543062</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.566939845508593</v>
+        <v>-1.577547595246777</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.816277043894381</v>
+        <v>-1.828064722801571</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.2472777022699972</v>
+        <v>-0.2540173394444096</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.8547163572789529</v>
+        <v>0.8504048475326584</v>
       </c>
     </row>
     <row r="19">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.1671</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4074~4087</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4074</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.2791001748710968</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.1532</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4040~4053</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4040</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.3098705926007952</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.1393</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4002~4015</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4002</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.2892041981676385</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.1254</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3957~3970</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3957</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.3271914688245872</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.1115</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3895~3907</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3895</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.1514879746763143</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.09762</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3804~3816</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3804</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.2921804585747552</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.08373</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3722~3734</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3722</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.3241828301189145</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.06984</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3600~3610</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3600</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.3881751623152425</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.05595</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3454~3464</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3454</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.4726531008104402</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.04206</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3236~3245</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3236</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.1667819257569647</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.02817</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2999~3007</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2999</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.08239741565393643</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.01428</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2684~2689</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2684</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.388673989198729</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.000389</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2300~2301</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2300</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.7877437745314424</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.0135</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1949~1949</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1949</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.996043465321073</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.02739</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1623~1623</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1623</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>2.46651238835441</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.04128</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1326~1326</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1326</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>2.559352026698022</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.05517</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1110~1110</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1110</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>3.722777896006242</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.06906</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>930~930</t>
-        </is>
+      <c r="B23" t="n">
+        <v>930</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>3.420540174413674</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.08296</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>772~772</t>
-        </is>
+      <c r="B24" t="n">
+        <v>772</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>3.594644581344426</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.09685</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>653~653</t>
-        </is>
+      <c r="B25" t="n">
+        <v>653</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>3.24928756034133</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.1107</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>540~540</t>
-        </is>
+      <c r="B26" t="n">
+        <v>540</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>3.802857976086322</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.1246</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>449~449</t>
-        </is>
+      <c r="B27" t="n">
+        <v>449</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>3.631283283353504</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.1385</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>374~374</t>
-        </is>
+      <c r="B28" t="n">
+        <v>374</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>3.92367397925527</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.1524</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>304~304</t>
-        </is>
+      <c r="B29" t="n">
+        <v>304</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>2.440772206105812</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.1663</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>243~243</t>
-        </is>
+      <c r="B30" t="n">
+        <v>243</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.1814587991315904</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.1802</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>198~198</t>
-        </is>
+      <c r="B31" t="n">
+        <v>198</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.041915215143561</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.1941</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>155~155</t>
-        </is>
+      <c r="B32" t="n">
+        <v>155</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.2353738040809432</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.208</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>125~125</t>
-        </is>
+      <c r="B33" t="n">
+        <v>125</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.306561679790029</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.2219</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>100~100</t>
-        </is>
+      <c r="B34" t="n">
+        <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>1.506561679790025</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.2358</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>2.268466441694791</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.1671</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>14.17322834645668</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.1532</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>118~118</t>
-        </is>
+      <c r="B7" t="n">
+        <v>118</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>11.06588371368833</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.1393</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>156~156</t>
-        </is>
+      <c r="B8" t="n">
+        <v>156</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>7.76297193620028</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.1254</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>201~201</t>
-        </is>
+      <c r="B9" t="n">
+        <v>201</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>6.710541779292512</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.1115</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>263~264</t>
-        </is>
+      <c r="B10" t="n">
+        <v>263</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>2.430804104032447</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.09762</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>354~355</t>
-        </is>
+      <c r="B11" t="n">
+        <v>354</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>3.281209567113969</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.08373</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>436~437</t>
-        </is>
+      <c r="B12" t="n">
+        <v>436</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>2.884136050499407</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.06984</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>558~561</t>
-        </is>
+      <c r="B13" t="n">
+        <v>558</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>2.586775583533338</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.05595</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>704~707</t>
-        </is>
+      <c r="B14" t="n">
+        <v>704</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.3863353714449</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.04206</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>922~926</t>
-        </is>
+      <c r="B15" t="n">
+        <v>922</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.6383111398332204</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.02817</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1159~1164</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1159</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.2557025732608196</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.01428</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1474~1482</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1474</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.6715759720318388</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.000389</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1858~1870</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1858</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.9426361811725457</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.0135</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2209~2222</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2209</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.728361812559214</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.02739</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2535~2548</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2535</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.551523092580467</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.04128</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2832~2845</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2832</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.175336386993813</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.05517</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3048~3061</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3048</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.333686605084196</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.06906</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3228~3241</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3228</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.9661319332923597</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.08296</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3386~3399</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3386</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.8017642984388687</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.09685</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3505~3518</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3505</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.5889471320348818</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.1107</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3618~3631</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3618</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.5518244397362722</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.1246</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3709~3722</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3709</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.4246580945248581</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.1385</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3784~3797</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3784</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.373343508516534</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.1524</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3854~3867</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3854</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.1789826698350083</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.1663</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3915~3928</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3915</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.001470030095525487</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.1802</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3960~3973</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3960</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.03937338187621719</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.1941</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4003~4016</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4003</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.02150191883385588</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.208</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4033~4046</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4033</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.002854314490960519</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.2219</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4058~4071</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4058</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.02475740642957902</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.2358</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4074~4087</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4074</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.0344219267673509</v>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_21.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_21.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-21 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-21 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>34</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.377149461245232</v>
+        <v>3.389633695057093</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.093125342841645</v>
+        <v>-4.080257595525737</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.37829825432371</v>
+        <v>1.391270309327361</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.425435211316</v>
+        <v>-1.412489543312745</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.962875740610102</v>
+        <v>-1.94979570818591</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-16.34305714159767</v>
+        <v>-16.33004861196899</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-16.43162316795478</v>
+        <v>-16.41858709407771</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-16.9020778536425</v>
+        <v>-16.88892311139553</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-19.90463720074251</v>
+        <v>-19.8914613431497</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-17.82060588713586</v>
+        <v>-17.80721876700331</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-12.15163103529977</v>
+        <v>-12.13818626024779</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-12.12034162267535</v>
+        <v>-12.10689765731771</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-9.603043278309379</v>
+        <v>-9.589491274153474</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.5321994762467952</v>
+        <v>-0.5426291119462832</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>38</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.486368237903541</v>
+        <v>-2.47388937642161</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.469200384727522</v>
+        <v>-1.456331485355243</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.633822235101903</v>
+        <v>8.646798647932663</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.76587177795799</v>
+        <v>8.778823177612338</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.353967293106308</v>
+        <v>0.3670480540494268</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.6514149865149079</v>
+        <v>0.6644312242594452</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5670192135588863</v>
+        <v>0.5800620326748245</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.526892517450683</v>
+        <v>-2.513732983918615</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.588364805572063</v>
+        <v>-2.57518407236978</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.819525842496354</v>
+        <v>1.832917458377572</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.615302861137657</v>
+        <v>1.628749946362213</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.64997493716956</v>
+        <v>1.663420444086853</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.492049470119916</v>
+        <v>6.505602395208975</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.374921266785933</v>
+        <v>9.36449163108778</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>45</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.051143134934229</v>
+        <v>3.063625632690716</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.52354171936644</v>
+        <v>12.53642042984134</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.13236119724276</v>
+        <v>12.14533954590578</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.61546888000386</v>
+        <v>5.628417811292387</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.080036237771459</v>
+        <v>5.093119085820355</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.814153089650247</v>
+        <v>9.827173446349718</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9.732075880637929</v>
+        <v>9.745122302466612</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>9.268173120725727</v>
+        <v>9.281336694968125</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.209667984618157</v>
+        <v>9.222852083511484</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.362586517613053</v>
+        <v>8.375979528106384</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.160026940079817</v>
+        <v>8.173475069539521</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>14.85965701165061</v>
+        <v>14.87310406636919</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>14.44322348656024</v>
+        <v>14.4567768620897</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>16.91878091590873</v>
+        <v>16.90835128021057</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-11.36533839959147</v>
+        <v>-11.17487146127809</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.352811411388501</v>
+        <v>-3.288897304898484</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.968606636251494</v>
+        <v>-6.849590607860982</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.620466091100752</v>
+        <v>-3.554768619364964</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6596665703803879</v>
+        <v>0.658590152746342</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.9589402096244086</v>
+        <v>0.9559588447389231</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.483212861121366</v>
+        <v>2.456161843142517</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.008231768021041</v>
+        <v>1.990598642066935</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.556475071336919</v>
+        <v>3.515580358649423</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.083322512117967</v>
+        <v>1.081655235856701</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.960398071481009</v>
+        <v>-3.880899537830658</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.9133818195965588</v>
+        <v>0.9118126249060623</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.325326732784532</v>
+        <v>5.252690428397557</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.03706048580046684</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>91</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.72976706652863</v>
+        <v>5.740702934656362</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.8372265477269636</v>
+        <v>0.8498376824701595</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6527661376934262</v>
+        <v>-0.6397032366278879</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.862290422226721</v>
+        <v>3.874142757448652</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.905795494892516</v>
+        <v>9.916214455646376</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>10.20568798728688</v>
+        <v>10.21601147982706</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.735106697968227</v>
+        <v>5.746631142175517</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.367657653235874</v>
+        <v>6.379162977241471</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.210714816846938</v>
+        <v>5.222566205515299</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.127598552331833</v>
+        <v>-1.113877091381354</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.529188387347283</v>
+        <v>-3.514762703503983</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-8.988917417751217</v>
+        <v>-8.973119477782518</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.213724299151437</v>
+        <v>-7.198303699557208</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-8.062904065776749</v>
+        <v>-8.073333701474901</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>82</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.160414991271374</v>
+        <v>1.172500765998485</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.661550032316221</v>
+        <v>-1.648283539825144</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.808897291982795</v>
+        <v>2.821035463533214</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5062386964454504</v>
+        <v>0.5189380611662742</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.402839558715428</v>
+        <v>2.415144680548977</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.60250403133594</v>
+        <v>-4.588336641967715</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.399672525405251</v>
+        <v>1.412288066698366</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.2842040914704711</v>
+        <v>-0.2709922309348158</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.745941569003342</v>
+        <v>5.757586808394294</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.461085593516323</v>
+        <v>2.473858595399868</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.694840631949219</v>
+        <v>4.707103497664562</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.072814623545291</v>
+        <v>1.086019670287776</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.225249359456988</v>
+        <v>-4.210544824120468</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.756015832058743</v>
+        <v>-2.766445467756895</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>122</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.564115496985764</v>
+        <v>1.576300588908452</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.707258506997078</v>
+        <v>-1.693714666253584</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.43779441200526</v>
+        <v>4.449676900459259</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.39033821045269</v>
+        <v>5.401912402684694</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.302327002660448</v>
+        <v>7.3134742933171</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.690111865478308</v>
+        <v>2.702567969832536</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1488509080666205</v>
+        <v>0.1620349394104821</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.3276358487335074</v>
+        <v>-0.3141600152114137</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.027797901878202</v>
+        <v>-2.013833424793724</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.895565684263055</v>
+        <v>-2.881086253186695</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.384493049918234</v>
+        <v>-6.368964897110715</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.886692287063148</v>
+        <v>-6.335336972062223</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-7.483945880848061</v>
+        <v>-7.936037580232835</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-7.234224548571774</v>
+        <v>-7.244654184269926</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>146</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.610364560714913</v>
+        <v>1.622264263015452</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.103283009120958</v>
+        <v>4.114943863952448</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9761321978442155</v>
+        <v>0.9886716644508198</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.311391053852923</v>
+        <v>-2.297955772296191</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.217187725525307</v>
+        <v>-4.203121009252271</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1832183789050035</v>
+        <v>0.1960963204506996</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.006033833468656</v>
+        <v>-3.991897209729821</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.052081470094379</v>
+        <v>-1.0386340093347</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.220519411614625</v>
+        <v>-5.205833081916971</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.126028235027405</v>
+        <v>-8.11021829142615</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.538676268704158</v>
+        <v>-3.524078895592268</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.559087631906827</v>
+        <v>-5.545635343186717</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.664273749701202</v>
+        <v>-6.650717703349599</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.784415431123229</v>
+        <v>-7.794845066821381</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>218</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.013016047934421</v>
+        <v>-4.999072597597831</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.054015482653675</v>
+        <v>-2.040521728497687</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.653696062024949</v>
+        <v>-5.639089435889098</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-8.271937644929885</v>
+        <v>-8.256537088644201</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.317925330208347</v>
+        <v>-3.30395176978724</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1855918186600292</v>
+        <v>0.1985271614205999</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.191660849350761</v>
+        <v>-2.177886407096963</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.119945555028622</v>
+        <v>-3.105751648788036</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.724508721161477</v>
+        <v>-2.71034712348969</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.663752398541938</v>
+        <v>-2.649278519254317</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.7738151401380122</v>
+        <v>-1.021115424197006</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2807163864624158</v>
+        <v>-0.2672640977423058</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.2422554010769318</v>
+        <v>-0.2286993547253289</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.827396454121853</v>
+        <v>-1.837826089820005</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>237</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.234584228706339</v>
+        <v>-1.22168736915107</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-7.90111677926042</v>
+        <v>-7.885596364207629</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-11.24691259383437</v>
+        <v>-11.2302087365097</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-10.27804973640738</v>
+        <v>-10.26161997724238</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-8.713218378896393</v>
+        <v>-8.697324181318955</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-9.872169725407637</v>
+        <v>-10.08771565472598</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.165891128498771</v>
+        <v>-6.150769288419845</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.743070906436827</v>
+        <v>-8.726934503388186</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.276155475471164</v>
+        <v>-6.260749029515182</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.862678507648724</v>
+        <v>-5.847062784938082</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-7.333254616776522</v>
+        <v>-7.319797323066304</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.611107746350733</v>
+        <v>-5.597655457630623</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.031362357295926</v>
+        <v>-6.017806310944323</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.781641025019447</v>
+        <v>-5.792070660717599</v>
       </c>
     </row>
     <row r="16">
@@ -1095,98 +1095,98 @@
         <v>315</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.096224877954064</v>
+        <v>-4.082083751175205</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.40978900035514</v>
+        <v>-5.394547882430118</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8477482733967605</v>
+        <v>0.8608258397382826</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.929588960649355</v>
+        <v>1.942298180032907</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.971187126614339</v>
+        <v>-1.132636894365</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.6733722367118418</v>
+        <v>-0.6603293404174764</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.535878182553972</v>
+        <v>-1.698016840300618</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4193329503902561</v>
+        <v>-0.4056208410546276</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1538307105985126</v>
+        <v>0.1673633979260103</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.5180934162283606</v>
+        <v>-0.6868046906918579</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.816835799136605</v>
+        <v>1.830293092846823</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6884635832005088</v>
+        <v>-0.6750112944803988</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.161123075695869</v>
+        <v>0.1746791220474719</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.811377814250072</v>
+        <v>-1.821807449948224</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.007334</t>
+          <t>X ≈ -0.007335</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>384</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.001587745866985</v>
+        <v>-2.126472121927257</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.00662621166706856</v>
+        <v>0.0202501006868161</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.847150674506011</v>
+        <v>-2.977464406170675</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4895549085035995</v>
+        <v>-0.6197128108633478</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.028945656958768</v>
+        <v>-1.015834852583829</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4706992392232792</v>
+        <v>-0.4576563429289138</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.380288689928044</v>
+        <v>-2.367222435627568</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.746380976923646</v>
+        <v>-3.879448066259748</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.92144045342252</v>
+        <v>-4.054598790817913</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.469482305117175</v>
+        <v>-3.456077177464344</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.195068962768026</v>
+        <v>-4.181611669057808</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.160685805422652</v>
+        <v>-4.147233516702542</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.497607083034161</v>
+        <v>-2.484051036682558</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.987469084091266</v>
+        <v>-1.997898719789418</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>351</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5.921589836149494</v>
+        <v>-5.909067546473871</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.24746207562437</v>
+        <v>-4.392541298439788</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.781931921822107</v>
+        <v>-5.768924790404505</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.645980783516599</v>
+        <v>-7.633001641118135</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.190100004286641</v>
+        <v>-6.176989199911702</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.898356072269117</v>
+        <v>-3.885313175974751</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.83779064424219</v>
+        <v>-4.824724389941714</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.025771763821538</v>
+        <v>-3.0125907545263</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.941472504704635</v>
+        <v>-3.928273765749871</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.79729569543062</v>
+        <v>-2.783890567777789</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.577547595246777</v>
+        <v>-1.564090301536559</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.828064722801571</v>
+        <v>-1.814612434081461</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.2540173394444096</v>
+        <v>-0.2404612930928067</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.8504048475326584</v>
+        <v>0.8399752118345063</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>326</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3461990564062276</v>
+        <v>-0.3336767667306049</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.723208925721472</v>
+        <v>1.736118735297524</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>6.543064145505255</v>
+        <v>6.556071276922857</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6.980065744370421</v>
+        <v>6.993044886768885</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5.828147596782841</v>
+        <v>5.841258401157781</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.205344135725568</v>
+        <v>5.218387032019933</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.734107350968557</v>
+        <v>5.747173605269033</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.653427019671817</v>
+        <v>4.666608028967055</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4.592427133489487</v>
+        <v>4.60562587244425</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.049050414719304</v>
+        <v>4.062455542372135</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.003806292855714</v>
+        <v>2.017263586565932</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.344937916458733</v>
+        <v>2.358390205178843</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.142801357062915</v>
+        <v>-1.129245310711312</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.9474107727594472</v>
+        <v>0.936981137061295</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>297</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.064538514920187</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.926560754723084</v>
+        <v>-2.913650945147033</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.341631481521624</v>
+        <v>-5.328624350104022</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-6.221479359015177</v>
+        <v>-6.208500216616713</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-5.413099227285997</v>
+        <v>-5.399988422911058</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.778956952869997</v>
+        <v>-4.765914056575632</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-6.210492016943661</v>
+        <v>-6.197425762643185</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.973971712021459</v>
+        <v>-2.960790702726221</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.708372271604397</v>
+        <v>-3.695173532649633</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.5281944263293</v>
+        <v>-1.514789298676469</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.059547077246194</v>
+        <v>-1.046089783535976</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.025163919900763</v>
+        <v>-1.011711631180653</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.09861718404432906</v>
+        <v>-0.08506113769272616</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.869097871970062</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>216</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.419364246135899</v>
+        <v>-3.406841956460276</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.790197118359366</v>
+        <v>-1.777287308783315</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.03691767680786</v>
+        <v>-4.023910545390258</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-5.295553433089246</v>
+        <v>-5.282574290690782</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.982122796309618</v>
+        <v>-3.969011991934678</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-6.925421599334648</v>
+        <v>-6.912378703040282</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.695340501792053</v>
+        <v>-4.682274247491577</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.236597974647637</v>
+        <v>-4.223416965352399</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.056857120089248</v>
+        <v>-1.043658381134485</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.36994526808013</v>
+        <v>-2.356540140427299</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.426550444249571</v>
+        <v>-4.413093150539353</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.318093212830057</v>
+        <v>-5.304640924109947</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.886495971923111</v>
+        <v>-3.872939925571508</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.173811676683854</v>
+        <v>-3.184241312382007</v>
       </c>
     </row>
     <row r="22">
@@ -1407,150 +1407,150 @@
         <v>180</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>5.284339457567867</v>
+        <v>5.29686174724349</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>8.11721028904806</v>
+        <v>8.130120098624111</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.722341582451342</v>
+        <v>2.735348713868945</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.852594715058899</v>
+        <v>2.865573857457363</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.574715388902092</v>
+        <v>-1.561604584527153</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.388384562297603</v>
+        <v>-2.375341666003237</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2508960573476031</v>
+        <v>-0.2378298030471271</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.9485872105375037</v>
+        <v>0.9617682198327415</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.2235237867558553</v>
+        <v>-0.2103250478010921</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.5930176948828247</v>
+        <v>0.6064228225356558</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.166042148343024</v>
+        <v>3.179499442053242</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.089314194577284</v>
+        <v>2.102766483297394</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.002392916965838765</v>
+        <v>0.01594896331744167</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.36322536035324</v>
+        <v>1.352795724655088</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.07601</t>
+          <t>X ≈ 0.076</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>158</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.569852819030459</v>
+        <v>2.582375108706081</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.9404549711489878</v>
+        <v>-0.9275451615729366</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.829233284279809</v>
+        <v>1.842240415697411</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.837981937543034</v>
+        <v>-1.82500279514457</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1552424170050202</v>
+        <v>0.1683532213799595</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.078961214899543</v>
+        <v>-2.065918318605178</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.633773422258443</v>
+        <v>1.646839676558919</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.529612508168618</v>
+        <v>-4.516431498873381</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.691878217135731</v>
+        <v>-2.678679478180968</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.154199129481981</v>
+        <v>2.167604257134812</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6836230203542826</v>
+        <v>0.6970803140645003</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.7180061776997775</v>
+        <v>0.7314584664198875</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.9306629591598323</v>
+        <v>0.9442190055114352</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.351261278184168</v>
+        <v>-1.36169091388232</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.08991</t>
+          <t>X ≈ 0.0899</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>119</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>5.489754957100956</v>
+        <v>5.502277246776579</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>10.60087041976694</v>
+        <v>10.61378022934299</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>6.844657175355231</v>
+        <v>6.857664306772833</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>12.85726324913914</v>
+        <v>12.87024239153761</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>8.957497496251897</v>
+        <v>8.970608300626836</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>9.254939433967515</v>
+        <v>9.26798233026188</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.489533447787721</v>
+        <v>7.502599702088197</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>10.38369458682134</v>
+        <v>10.39687559611658</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.121014028370141</v>
+        <v>6.134212767324904</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.791897246703506</v>
+        <v>7.805302374356337</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.906471653478413</v>
+        <v>5.91992894718863</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.940854810823843</v>
+        <v>5.954307099543954</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.839927930971328</v>
+        <v>3.853483977322931</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.929985397701451</v>
+        <v>4.919555762003299</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>113</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6039068125333955</v>
+        <v>0.6164291022090183</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.956934969480685</v>
+        <v>6.969844779056736</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.137287501822151</v>
+        <v>2.150294633239753</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3873266222075742</v>
+        <v>-0.37434747980911</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.8441636671450894</v>
+        <v>0.8572744715200287</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.911517109285477</v>
+        <v>2.924560005579842</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.36660640086275</v>
+        <v>6.379672655163226</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.014467249868872</v>
+        <v>5.02764825916411</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.298600107049346</v>
+        <v>2.311798846004109</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.33343067423386</v>
+        <v>2.346835801886691</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.898588854341007</v>
+        <v>3.912046148051225</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.587839268323656</v>
+        <v>6.601291557043766</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.397673152953971</v>
+        <v>4.411229199305573</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.762438733017824</v>
+        <v>3.752009097319672</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>91</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.649418822647128</v>
+        <v>4.661941112322751</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.23564740748504</v>
+        <v>5.248557217061091</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.752627892518142</v>
+        <v>-1.739620761100539</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5234736610094757</v>
+        <v>-0.5104945186110115</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.43261061842378</v>
+        <v>4.445721422798719</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>8.026755852842804</v>
+        <v>8.039798749137169</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.84312103666943</v>
+        <v>6.856187290969906</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.178135440085796</v>
+        <v>4.191316449381034</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.314937751705685</v>
+        <v>6.328136490660448</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.464812566677757</v>
+        <v>5.478217694330588</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.161158143459147</v>
+        <v>4.174615437169365</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.8988380041010942</v>
+        <v>0.9122902928212042</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.577484492057415</v>
+        <v>1.591040538409018</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.222810219938104</v>
+        <v>6.212380584239952</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>75</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.173228346456732</v>
+        <v>2.185750636132354</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.105011933174232</v>
+        <v>-2.092102123598181</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.036294173829987</v>
+        <v>-1.023315031431522</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.574715388902156</v>
+        <v>-1.561604584527217</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.05605988214679769</v>
+        <v>0.06910277844116308</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.97132616487459</v>
+        <v>3.984392419175066</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.837476099426311</v>
+        <v>4.850657108721549</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.109809546577459</v>
+        <v>6.123008285532222</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.593017694882825</v>
+        <v>2.606422822535656</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.611735629434833</v>
+        <v>-1.598278335724615</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.755980861244055</v>
+        <v>3.769433149964165</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.002392916965697</v>
+        <v>2.0159489633173</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.918780915908727</v>
+        <v>4.908351280210574</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>70</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10.36370453693288</v>
+        <v>10.3762268266085</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>11.60927378111148</v>
+        <v>11.62218359068753</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>15.50011936022918</v>
+        <v>15.51312649164678</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>17.05894392140811</v>
+        <v>17.07192306380657</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>16.52052270633594</v>
+        <v>16.53363351071088</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>12.53225035833735</v>
+        <v>12.54529325463172</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>12.447516641065</v>
+        <v>12.46058289536548</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>16.26604752799782</v>
+        <v>16.27922853729306</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>14.77647621324405</v>
+        <v>14.78967495219881</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>13.92635102821616</v>
+        <v>13.93975615586899</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>15.15016913247001</v>
+        <v>15.16362642618023</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>13.7559808612441</v>
+        <v>13.76943314996421</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>16.19286910744196</v>
+        <v>16.20642515379356</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>13.5854475825754</v>
+        <v>13.57501794687725</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>61</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>11.44098790929823</v>
+        <v>11.45351019897385</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>11.4687585586291</v>
+        <v>11.48166836820515</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>17.63126690121274</v>
+        <v>17.64427403263034</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>12.84348724693503</v>
+        <v>12.8564663893335</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>9.026377507272755</v>
+        <v>9.039488311647695</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.323819444988317</v>
+        <v>9.336862341282682</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12.51777425230625</v>
+        <v>12.53084050660672</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>12.05059085352479</v>
+        <v>12.06377186282003</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>15.26827949193261</v>
+        <v>15.28147823088737</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.500121520019391</v>
+        <v>9.513526647672222</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>14.21340098258706</v>
+        <v>14.22685827629728</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>14.24778413993253</v>
+        <v>14.26123642865264</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>15.46687379128272</v>
+        <v>15.48042983763432</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>9.159218074378671</v>
+        <v>9.148788438680519</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>45</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.60454943132109</v>
+        <v>-3.592027141645467</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.894988066825711</v>
+        <v>5.907897876401762</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>18.83345269356261</v>
+        <v>18.84645982498021</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>14.51926138172556</v>
+        <v>14.53224052412403</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>16.20306238887559</v>
+        <v>16.21617319325053</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>18.72272654881357</v>
+        <v>18.73576944510793</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16.41577060931903</v>
+        <v>16.42883686361951</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>20.39303165498188</v>
+        <v>20.40621266427711</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>20.33203176879965</v>
+        <v>20.34523050775441</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>17.25968436154956</v>
+        <v>17.27308948920239</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>19.2771532594542</v>
+        <v>19.29061055316441</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>19.3115364167995</v>
+        <v>19.32498870551961</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>18.89128180585467</v>
+        <v>18.90483785220627</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>14.69655869368651</v>
+        <v>14.68612905798836</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>43</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.646096563510959</v>
+        <v>5.658618853186582</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.034522950546702</v>
+        <v>4.047432760122753</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.011508546747606</v>
+        <v>-0.9985014153300042</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.881255414140071</v>
+        <v>-0.8682762717416068</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.745258024561103</v>
+        <v>-3.732147220186164</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.12223469149658</v>
+        <v>-1.109191795202214</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.444194381928789</v>
+        <v>3.457260636229265</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.628173773844992</v>
+        <v>7.64135478314023</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.892755283011574</v>
+        <v>9.905954021966338</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.042630097983604</v>
+        <v>9.056035225636435</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.186713982968378</v>
+        <v>4.200171276678596</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>13.52342272170917</v>
+        <v>13.53687501042928</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>13.10316811076422</v>
+        <v>13.11672415711583</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>18.00405223373819</v>
+        <v>17.99362259804004</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>30</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.493438320210025</v>
+        <v>-2.480916030534402</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.105011933174282</v>
+        <v>-4.092102123598231</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-7.833213973104158</v>
+        <v>-7.820206841686556</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.091951277764551</v>
+        <v>5.10506208213949</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.722726548813498</v>
+        <v>8.735769445107863</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.304659498207933</v>
+        <v>5.317725752508409</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.504142766093054</v>
+        <v>1.517323775388292</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.776476213244038</v>
+        <v>4.789674952198801</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.72159770389854</v>
+        <v>13.73505499760876</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>20.42264752791063</v>
+        <v>20.43609981663074</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>26.66905958363245</v>
+        <v>26.68261562998406</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>30.25211424924207</v>
+        <v>30.24168461354392</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>25</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.493438320209918</v>
+        <v>-4.480916030534296</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-14.1050119331742</v>
+        <v>-14.09210212359815</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.500119360229206</v>
+        <v>1.513126491646808</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>9.630372492836678</v>
+        <v>9.643351635235142</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9.091951277764423</v>
+        <v>9.105062082139362</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>13.38939321548017</v>
+        <v>13.40243611177453</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.304659498207862</v>
+        <v>1.317725752508338</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.837476099426418</v>
+        <v>4.850657108721656</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.776476213244116</v>
+        <v>4.78967495219888</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.92635102821616</v>
+        <v>7.939756155868992</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2784022961014117</v>
+        <v>-0.2649450023911939</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2440191387559807</v>
+        <v>-0.2305668500358706</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.335726250299111</v>
+        <v>7.349282296650713</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.585447582575426</v>
+        <v>7.575017946877274</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>16</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.14498806682581</v>
+        <v>2.157897876401861</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-10.74988063977086</v>
+        <v>-10.73687350835326</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.130372492836678</v>
+        <v>8.143351635235142</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.591951277764551</v>
+        <v>7.60506208213949</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>14.13939321548017</v>
+        <v>14.15243611177453</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>20.30465949820785</v>
+        <v>20.31772575250832</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>26.08747609942635</v>
+        <v>26.10065710872158</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>13.52647621324405</v>
+        <v>13.53967495219881</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>18.92635102821616</v>
+        <v>18.93975615586899</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>18.72159770389862</v>
+        <v>18.73505499760884</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.50598086124401</v>
+        <v>12.51943314996412</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>24.58572625029911</v>
+        <v>24.59928229665071</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.58544758257536</v>
+        <v>18.5750179468772</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-21 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-21 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2791001748710968</v>
+        <v>-0.2793504728044098</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.09130659788299056</v>
+        <v>-0.09161276710197797</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1547154010927301</v>
+        <v>-0.1550086038010932</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2070418068694906</v>
+        <v>-0.2073215593793023</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1688863416329909</v>
+        <v>-0.1691788581152025</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.05401687761145268</v>
+        <v>-0.05433586961169823</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.0273669658940463</v>
+        <v>-0.02769315978952847</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.03355453079894488</v>
+        <v>0.03321040448246748</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1086654753181264</v>
+        <v>0.1083024031792448</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1058507829979192</v>
+        <v>0.1054830497155237</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1356276278622772</v>
+        <v>0.1352511722041854</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.0611820388691342</v>
+        <v>0.06082387844094228</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1210023239187379</v>
+        <v>0.1206267519990973</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1146572045685232</v>
+        <v>0.1148952474907432</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4040</v>
+        <v>4041</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3098705926007952</v>
+        <v>-0.3102204212595652</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.05762792527689697</v>
+        <v>-0.0580532708964796</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1676170011630731</v>
+        <v>-0.1680186218774082</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1967880009904803</v>
+        <v>-0.1971815664434615</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1537884110475431</v>
+        <v>-0.154197177119805</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.08306910480823149</v>
+        <v>0.08260405447644104</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1106886556084419</v>
+        <v>0.110215871085444</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1760821300739437</v>
+        <v>0.1755891571525652</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.2770942602156623</v>
+        <v>0.2765755948088326</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2567170024990517</v>
+        <v>0.2561962053127544</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2390352502750304</v>
+        <v>0.2385169165009842</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1636998122583648</v>
+        <v>0.1632001546635991</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2028383512642193</v>
+        <v>0.2023253446467592</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1201010479219278</v>
+        <v>0.1204274989683114</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2892041981676385</v>
+        <v>-0.2896809707733965</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.044224688530484</v>
+        <v>-0.04477958312494934</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2511888879641901</v>
+        <v>-0.2516966274364307</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2818907175322209</v>
+        <v>-0.2823897054077733</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1586096796027263</v>
+        <v>-0.1591452957269581</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.07767251722580681</v>
+        <v>0.07708083877527372</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1063556817948239</v>
+        <v>0.1057556776953987</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2017475565122098</v>
+        <v>0.2011185704327829</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3043025172121432</v>
+        <v>0.3036470080870757</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2418777381512527</v>
+        <v>0.2412285791282827</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2259672419759866</v>
+        <v>0.2253196007041538</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1495872548504096</v>
+        <v>0.1489587429728587</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1431207044584895</v>
+        <v>0.1424890898575129</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.03222419426954559</v>
+        <v>0.03267470430917285</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3957</v>
+        <v>3958</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3271914688245872</v>
+        <v>-0.3278059826874653</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1871484915012687</v>
+        <v>-0.1878200077291652</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3920177365450073</v>
+        <v>-0.3926432236467434</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3489569752752431</v>
+        <v>-0.3495919131519614</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2181848795728598</v>
+        <v>-0.2188602773261508</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.03305319057279377</v>
+        <v>-0.03377165423655981</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.003110431156393645</v>
+        <v>-0.003837929711053789</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.09864188292373655</v>
+        <v>0.09788213394867284</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2030284595843241</v>
+        <v>0.2022411898975633</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1495269938814019</v>
+        <v>0.1487415167978128</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1357391180400001</v>
+        <v>0.1349540130089579</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.01769936103434588</v>
+        <v>-0.01844563791466669</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.01950366379891477</v>
+        <v>-0.02025546541041479</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.159813979213844</v>
+        <v>-0.1591912496866783</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3895</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1514879746763143</v>
+        <v>-0.1523592239836873</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1367579649202639</v>
+        <v>-0.1376613762216721</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2873326244059058</v>
+        <v>-0.2882047935554723</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2968816055239785</v>
+        <v>-0.2977495171336173</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.232158381471983</v>
+        <v>-0.2330526719589088</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.04884358616001805</v>
+        <v>-0.04978013214039834</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.04268733593719531</v>
+        <v>-0.04362739972125951</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.06824533019561585</v>
+        <v>0.0672682340741062</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1496488216052114</v>
+        <v>0.1486493111732088</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.134662983064807</v>
+        <v>0.1336520266050769</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2009407883224981</v>
+        <v>0.1999087687735042</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.03252016545003755</v>
+        <v>-0.03349217721062558</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1045818369922884</v>
+        <v>-0.1055431653616097</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1629477961152332</v>
+        <v>-0.1733774318133854</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3804</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2921804585747552</v>
+        <v>-0.2933341599553572</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1600578047338601</v>
+        <v>-0.1612845135352856</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2785906555023416</v>
+        <v>-0.2797961820098394</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3963780972498725</v>
+        <v>-0.3975503049850957</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4746804116373866</v>
+        <v>-0.4758453398379956</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2941544098150288</v>
+        <v>-0.2953603205444608</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1809048062540555</v>
+        <v>-0.1821430483313051</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.08245039046597213</v>
+        <v>-0.08372609337811099</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.02857705358022855</v>
+        <v>0.02727012153463448</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1648590397738161</v>
+        <v>0.1634956516673114</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2901736366363679</v>
+        <v>0.2887718350135771</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1817364460009117</v>
+        <v>0.1803632603161986</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.06548439961562025</v>
+        <v>0.06413117969933069</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.0260364364134702</v>
+        <v>0.01560680071531806</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>3722</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3241828301189145</v>
+        <v>-0.3256282125959302</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1269781801605703</v>
+        <v>-0.1285241910861288</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3466116151191585</v>
+        <v>-0.3481111188541561</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.416263797702058</v>
+        <v>-0.4177416123532822</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5380755318869603</v>
+        <v>-0.5395372209964435</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1992364439459493</v>
+        <v>-0.2007810464024118</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2157267678865367</v>
+        <v>-0.217270224965489</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.07800552118000326</v>
+        <v>-0.07960040200798346</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.09738315336890224</v>
+        <v>-0.09897543685400478</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1142704913034009</v>
+        <v>0.1125956620418336</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1931336867127627</v>
+        <v>0.1914308365349768</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.162104954717023</v>
+        <v>0.1604105935731468</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.1600142674941694</v>
+        <v>0.1583072765056741</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.08732829187147928</v>
+        <v>0.07689865617332714</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>3600</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3881751623152425</v>
+        <v>-0.390082466424694</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.07342423575111923</v>
+        <v>-0.07548162498322597</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.5087498193717082</v>
+        <v>-0.5107028239531033</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.6130430879784043</v>
+        <v>-0.6149632206406821</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.8037780622244028</v>
+        <v>-0.8056670556481862</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2971532477653227</v>
+        <v>-0.2991723186192559</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.228081900238287</v>
+        <v>-0.2301244555360142</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.06954582674624277</v>
+        <v>-0.07165143733830348</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.03196354244720112</v>
+        <v>-0.03408302726271017</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2162704950309333</v>
+        <v>0.2140482158356818</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4160421483430312</v>
+        <v>0.4137553586196248</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3670919723551265</v>
+        <v>0.3805442610752365</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4190595836324391</v>
+        <v>0.432615629984042</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.335447582575398</v>
+        <v>0.3250179468772458</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3454</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4726531008104402</v>
+        <v>-0.4751440247623435</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2499729496339498</v>
+        <v>-0.2526102067390497</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.5715155328961785</v>
+        <v>-0.5740811318011012</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5412542046496043</v>
+        <v>-0.5438234080924147</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6594938089406952</v>
+        <v>-0.6620572475340509</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3174584757600769</v>
+        <v>-0.3201072408266157</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.06838850641905481</v>
+        <v>-0.07111495289782255</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.02801421009053229</v>
+        <v>-0.03077724639693713</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.1873558428737141</v>
+        <v>0.1845259791007905</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5688980615012582</v>
+        <v>0.5659135632763963</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.5832074317503526</v>
+        <v>0.580206951299111</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6175905890957836</v>
+        <v>0.6310428778158936</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.7184708941902471</v>
+        <v>0.73202694054185</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6786728286668833</v>
+        <v>0.6682431929687311</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>3236</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1667819257569647</v>
+        <v>-0.1703799861720654</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1284398000053031</v>
+        <v>-0.1321637568801535</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2291436678312664</v>
+        <v>-0.2328661100794776</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.02046032641069928</v>
+        <v>-0.02424010081173122</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.48040293389856</v>
+        <v>-0.484080422487331</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3513475252605716</v>
+        <v>-0.3550461467876431</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.07465023608994414</v>
+        <v>0.07081217226144787</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1802802995499206</v>
+        <v>0.1763749228617897</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3835197720948784</v>
+        <v>0.3795452425015071</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.78667241264138</v>
+        <v>0.7825117938053481</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6746261340592739</v>
+        <v>0.6880834277694916</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.6781069428262185</v>
+        <v>0.6915592315463286</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7831922577156689</v>
+        <v>0.7967483040672718</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.8474994985210103</v>
+        <v>0.8370698628228581</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2999</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.08239741565393643</v>
+        <v>-0.08729900925775524</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4858064300992169</v>
+        <v>0.4805616609046481</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.6415503086484762</v>
+        <v>0.6362136506620857</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7901594435690384</v>
+        <v>0.7847825836544402</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1702063560195839</v>
+        <v>0.1649821886640765</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4010482271351847</v>
+        <v>0.4140911234295501</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5678173929447397</v>
+        <v>0.5624809972636058</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.8854601047579393</v>
+        <v>0.8799708995277626</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9098095465774207</v>
+        <v>0.9043034093797857</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.312146293304515</v>
+        <v>1.306422822535659</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.307459657883243</v>
+        <v>1.32091695159346</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.175120574481753</v>
+        <v>1.188572863201863</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.321721582076371</v>
+        <v>1.335277628427974</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.371376225456352</v>
+        <v>1.3609465897582</v>
       </c>
     </row>
     <row r="17">
@@ -2789,98 +2789,98 @@
         <v>2684</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.388673989198729</v>
+        <v>0.3815375010641517</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.177726162063863</v>
+        <v>1.170077125193195</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6173504729943389</v>
+        <v>0.6098526821229697</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.656433550171009</v>
+        <v>0.6489340691763417</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3041627446297355</v>
+        <v>0.3172735490046747</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.5271445185330279</v>
+        <v>0.5401874148273933</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.8147116203225622</v>
+        <v>0.8277778746230382</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.038593417862145</v>
+        <v>1.030850705147536</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.9985328451367934</v>
+        <v>0.9907922706346071</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.526947153402446</v>
+        <v>1.540352281055277</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.247678180798736</v>
+        <v>1.261135474508954</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.393834810573367</v>
+        <v>1.407287099293477</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.457931913488387</v>
+        <v>1.47148795983999</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.744911069907737</v>
+        <v>1.734481434209584</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.000389</t>
+          <t>X &gt; -0.0003892</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2300</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7877437745314424</v>
+        <v>0.8002660642070651</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.373248936390986</v>
+        <v>1.362048245806427</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.195771534142224</v>
+        <v>1.208778665559826</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8477637971845056</v>
+        <v>0.8607429395829698</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5267338864601641</v>
+        <v>0.5398446908351033</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.6937410415671224</v>
+        <v>0.7067839378614877</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.348137759077453</v>
+        <v>1.361204013377929</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.837476099426382</v>
+        <v>1.85065710872162</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.819954474113651</v>
+        <v>1.833153213068414</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.361133636911816</v>
+        <v>2.374538764564647</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.156380312594237</v>
+        <v>2.169837606304455</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.321198252548356</v>
+        <v>2.334650541268466</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.118334945951283</v>
+        <v>2.131890992302885</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.36805627822757</v>
+        <v>2.357626642529418</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>1949</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.996043465321073</v>
+        <v>2.008565754996695</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.385496019622074</v>
+        <v>2.398405829198126</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.452402582394392</v>
+        <v>2.465409713811994</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.377422261949043</v>
+        <v>2.390401404347507</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.736384320350446</v>
+        <v>1.749495124725385</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.520742625433989</v>
+        <v>1.533785521728355</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.462176173425945</v>
+        <v>2.475242427726421</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.713309860329417</v>
+        <v>2.726490869624655</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.857543427199964</v>
+        <v>2.870742166154727</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.290127323752337</v>
+        <v>3.303532451405168</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.828832183118699</v>
+        <v>2.842289476828917</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.068448793516971</v>
+        <v>3.081901082237081</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.545577456045642</v>
+        <v>2.559133502397245</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.641373698532298</v>
+        <v>2.630944062834146</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>1623</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.46651238835441</v>
+        <v>2.479034678030033</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.518524727331005</v>
+        <v>2.531434536907057</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.630741664603789</v>
+        <v>1.643748796021391</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.452923324629651</v>
+        <v>1.465902467028116</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9145021095574819</v>
+        <v>0.9276129139324212</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7806439856588483</v>
+        <v>0.7936868819532137</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.804967569680471</v>
+        <v>1.818033823980947</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.323612883160209</v>
+        <v>2.336793892455447</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.509070175043227</v>
+        <v>2.522268913997991</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.137688058407164</v>
+        <v>3.151093186059995</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.994549028605917</v>
+        <v>3.008006322316135</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.213775069500329</v>
+        <v>3.227227358220439</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.286434814686046</v>
+        <v>3.299990861037649</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.981627496315383</v>
+        <v>2.971197860617231</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>1326</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.559352026698022</v>
+        <v>2.571874316373645</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.738125321727736</v>
+        <v>3.751035131303787</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.192427052536864</v>
+        <v>3.205434183954466</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.171850622550096</v>
+        <v>3.18482976494856</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.331770282289391</v>
+        <v>2.34488108666433</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.02589396962798</v>
+        <v>2.038936865922345</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.600285440892662</v>
+        <v>3.613351695193138</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.510175948596832</v>
+        <v>3.523356957892069</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.901664750197334</v>
+        <v>3.914863489152097</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.182761284626416</v>
+        <v>4.196166412279247</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.902593179011703</v>
+        <v>3.916050472721921</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.163220680248536</v>
+        <v>4.176672968968646</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.04462519449217</v>
+        <v>4.058181240843773</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.068102182877055</v>
+        <v>4.057672547178903</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1110</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.722777896006242</v>
+        <v>3.735300185681865</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.813906985744687</v>
+        <v>4.826816795320738</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.59921845932827</v>
+        <v>4.612225590745872</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.819561682025864</v>
+        <v>4.832540824424328</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.560419746232981</v>
+        <v>3.57353055060792</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.767771593858548</v>
+        <v>3.780814490152913</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5.214569408117796</v>
+        <v>5.227635662418272</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>5.017656279606562</v>
+        <v>5.0308372889018</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.866566303334174</v>
+        <v>4.879765042288938</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>5.457882559747695</v>
+        <v>5.471287687400526</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>5.523399505700382</v>
+        <v>5.5368567994106</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>6.00823311349626</v>
+        <v>6.02168540221637</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5.587978502551358</v>
+        <v>5.601534548902961</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5.477339474467293</v>
+        <v>5.466909838769141</v>
       </c>
     </row>
     <row r="23">
@@ -3101,98 +3101,98 @@
         <v>930</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.420540174413674</v>
+        <v>3.433062464089296</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.17455795929888</v>
+        <v>4.187467768874932</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.962484951627026</v>
+        <v>4.975492083044628</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.200264965954958</v>
+        <v>5.213244108353422</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.554316869162356</v>
+        <v>4.567427673537296</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.959285688598449</v>
+        <v>4.972328584892814</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6.272401433691755</v>
+        <v>6.285467687992231</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.805218034910254</v>
+        <v>5.818399044205492</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.851745030448384</v>
+        <v>5.864943769403148</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>6.399469307786056</v>
+        <v>6.412874435438887</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.979662220027613</v>
+        <v>5.993119513737831</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.76673354941606</v>
+        <v>6.78018583813617</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6.669059583632439</v>
+        <v>6.682615629984042</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6.273619625586143</v>
+        <v>6.263189989887991</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.08296</t>
+          <t>X &gt; 0.08295</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>772</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.594644581344426</v>
+        <v>3.607166871020048</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5.221412937292087</v>
+        <v>5.234322746868138</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.60374630323436</v>
+        <v>5.616753434651962</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.640735187137189</v>
+        <v>6.653714329535653</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.454645578282644</v>
+        <v>5.467756382657583</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.39975590978068</v>
+        <v>6.412798806075045</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.221757943803745</v>
+        <v>7.234824198104221</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>7.920377653830535</v>
+        <v>7.933558663125773</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>7.600310410135279</v>
+        <v>7.613509149090042</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.26831994013326</v>
+        <v>7.281725067786091</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>7.063566615815681</v>
+        <v>7.077023909525899</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>8.004685524456448</v>
+        <v>8.018137813176558</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.843498271024494</v>
+        <v>7.857054317376097</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.834152245787834</v>
+        <v>7.823722610089682</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>653</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.24928756034133</v>
+        <v>3.261809850016952</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.241083013226998</v>
+        <v>4.253992822803049</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.377607874777418</v>
+        <v>5.39061500619502</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.507861007384918</v>
+        <v>5.520840149783382</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.816300435498043</v>
+        <v>4.829411239872982</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5.879439157287216</v>
+        <v>5.892482053581581</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.172959651347249</v>
+        <v>7.186025905647725</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.471473036639253</v>
+        <v>7.484654045934491</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.86989122090106</v>
+        <v>7.883089959855823</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.172905392687838</v>
+        <v>7.186310520340669</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.274430781999648</v>
+        <v>7.287888075709866</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.380789437047994</v>
+        <v>8.394241725768104</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8.573092253361899</v>
+        <v>8.586648299713502</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>8.363395515194085</v>
+        <v>8.352965879495933</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>540</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.802857976086322</v>
+        <v>3.815380265761945</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.672765844603539</v>
+        <v>3.68567565417959</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.055674915784728</v>
+        <v>6.06868204720233</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.741483603947792</v>
+        <v>6.754462746346256</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.647506833320058</v>
+        <v>5.660617637694997</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.500504326591283</v>
+        <v>6.513547222885649</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.341696535244928</v>
+        <v>7.354762789545404</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>7.985624247574542</v>
+        <v>7.99880525686978</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>9.035735472503355</v>
+        <v>9.048934211458118</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.185610287475427</v>
+        <v>8.199015415128258</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.980856963157848</v>
+        <v>7.994314256868066</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.755980861244012</v>
+        <v>8.769433149964122</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9.446837361410225</v>
+        <v>9.460393407761828</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.326188323316146</v>
+        <v>9.315758687617993</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>449</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.631283283353504</v>
+        <v>3.643805573029127</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.356012565712184</v>
+        <v>3.368922375288236</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>7.638203992745879</v>
+        <v>7.651211124163481</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.213891423794358</v>
+        <v>8.226870566192822</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.893733014958272</v>
+        <v>5.906843819333211</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.191174952673933</v>
+        <v>6.204217848968298</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.442744130724591</v>
+        <v>7.455810385025067</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.757297925707007</v>
+        <v>8.770478935002245</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>9.587166636406671</v>
+        <v>9.600365375361434</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.737041451378744</v>
+        <v>8.750446579031575</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.755005276281651</v>
+        <v>8.768462569991868</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>10.34840847817053</v>
+        <v>10.36186076689064</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.04173961332805</v>
+        <v>11.05529565967966</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>9.955158050281412</v>
+        <v>9.94472841458326</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>374</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.92367397925527</v>
+        <v>3.936196268930892</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.451137799446087</v>
+        <v>4.464047609022138</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.06696428001527</v>
+        <v>8.079971411432872</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.06887516663347</v>
+        <v>10.08185430903193</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7.391416518406224</v>
+        <v>7.404527322781163</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.421478776977501</v>
+        <v>7.434521673271867</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8.138884097138366</v>
+        <v>8.151950351438842</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.543358452367563</v>
+        <v>9.556539461662801</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>10.28449760361841</v>
+        <v>10.29769634257318</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.969131776879266</v>
+        <v>9.982536904532097</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.83389716913922</v>
+        <v>10.84735446284944</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.67041936391782</v>
+        <v>11.68387165263793</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>12.85444282783921</v>
+        <v>12.86799887419082</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.96512672696042</v>
+        <v>10.95469709126227</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>304</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.440772206105812</v>
+        <v>2.453294495781435</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.80288280366787</v>
+        <v>2.815792613243921</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>6.355382518123911</v>
+        <v>6.368389649541513</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.459319861257725</v>
+        <v>8.47229900365619</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.289319698817138</v>
+        <v>5.302430503192078</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.244656373374902</v>
+        <v>6.257699269669267</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.146764761365787</v>
+        <v>7.159831015666263</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.995370836268492</v>
+        <v>8.00855184556373</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.250160423770403</v>
+        <v>9.263359162725166</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.057929975584585</v>
+        <v>9.071335103237416</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.840018756530156</v>
+        <v>9.853476050240374</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.19019138755979</v>
+        <v>11.2036436762799</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.08572625029911</v>
+        <v>12.09928229665071</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.36176337204908</v>
+        <v>10.35133373635093</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>243</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1814587991315904</v>
+        <v>0.1939810888072131</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.6274983548916069</v>
+        <v>0.640408164467658</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.524810718253875</v>
+        <v>3.537817849671477</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.35876755456507</v>
+        <v>7.371746696963534</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.351210537023761</v>
+        <v>4.3643213413987</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.471697742229146</v>
+        <v>5.484740638523512</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.798486658701719</v>
+        <v>5.811552913002195</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.977393794899633</v>
+        <v>6.990574804194871</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.73943917620705</v>
+        <v>7.752637915161813</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.94692715990341</v>
+        <v>8.960332287556241</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.742173835585831</v>
+        <v>8.755631129296049</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.23696081820035</v>
+        <v>11.25051686455195</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.66363688298692</v>
+        <v>10.65320724728877</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>198</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.041915215143561</v>
+        <v>1.054437504819184</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.5696583978206959</v>
+        <v>-0.5567485882446448</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>0.05858103710131957</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.731382593846774</v>
+        <v>5.744361736245239</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.657607843421069</v>
+        <v>1.670718647796008</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.460100286187242</v>
+        <v>2.473143182481607</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.385467579015966</v>
+        <v>3.398533833316442</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.928385190335483</v>
+        <v>3.941566199630721</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.877486314254185</v>
+        <v>4.890685053208948</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.057664159529288</v>
+        <v>7.071069287182119</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.347860330161211</v>
+        <v>6.361317623871429</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.402445507708663</v>
+        <v>8.415897796428773</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.497342411915277</v>
+        <v>9.51089845826688</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.747063744191564</v>
+        <v>9.736634108493412</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>155</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2353738040809432</v>
+        <v>-0.2228515144053205</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.8469474170452</v>
+        <v>-1.834037607469149</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.3388290376485301</v>
+        <v>0.3518361690661322</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.565856363804421</v>
+        <v>7.578835506202886</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.156467406796772</v>
+        <v>3.169578211171711</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.453909344512432</v>
+        <v>3.466952240806798</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.369175627240153</v>
+        <v>3.382241881540629</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.901992228458653</v>
+        <v>2.915173237753891</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.486153632598921</v>
+        <v>3.499352371553684</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.506996189506488</v>
+        <v>6.520401317159319</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.947404155511478</v>
+        <v>6.960861449221696</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.981787312856909</v>
+        <v>6.995239601577019</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>8.497016572879751</v>
+        <v>8.510572619231354</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.456415324510878</v>
+        <v>7.445985688812726</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>125</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.306561679790029</v>
+        <v>0.3190839694656518</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.305011933174228</v>
+        <v>-1.292102123598177</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.300119360229175</v>
+        <v>2.313126491646777</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.030372492836676</v>
+        <v>8.04335163523514</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.691951277764502</v>
+        <v>2.705062082139442</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.189393215480166</v>
+        <v>2.202436111774531</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.904659498207884</v>
+        <v>2.91772575250836</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.237476099426388</v>
+        <v>3.250657108721626</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.176476213244086</v>
+        <v>3.18967495219885</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.526351028216162</v>
+        <v>5.539756155868993</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.321597703898583</v>
+        <v>5.3350549976088</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.135726250299108</v>
+        <v>4.149282296650711</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.985447582575397</v>
+        <v>1.975017946877244</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.506561679790025</v>
+        <v>1.519083969465647</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.894988066825775</v>
+        <v>1.907897876401826</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.500119360229171</v>
+        <v>2.513126491646773</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.630372492836678</v>
+        <v>7.643351635235142</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.091951277764515</v>
+        <v>1.105062082139455</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.6106067845198311</v>
+        <v>-0.5975638882254657</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.304659498207883</v>
+        <v>3.317725752508359</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.837476099426382</v>
+        <v>2.85065710872162</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.776476213244081</v>
+        <v>2.789674952198844</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.92635102821616</v>
+        <v>4.939756155868992</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.721597703898581</v>
+        <v>6.735054997608799</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.755980861244012</v>
+        <v>4.769433149964122</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.5854475825753909</v>
+        <v>0.5750179468772387</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.280988731370414</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.847369019206724</v>
+        <v>1.860278828782775</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5.023928884038703</v>
+        <v>5.036936015456305</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.535134397598583</v>
+        <v>7.548113539997047</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1461439603307255</v>
+        <v>-0.1330331559557862</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-3.420130594043641</v>
+        <v>-3.407087697749276</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.06656426011265637</v>
+        <v>0.0796305144131324</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-1.591095329145041</v>
+        <v>-1.577914319849803</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.728857165625044</v>
+        <v>0.7420559045798072</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>2.259684361549496</v>
+        <v>2.273089489202327</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.435883418184289</v>
+        <v>4.449340711894507</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3.279790385053538</v>
+        <v>3.293242673773648</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.7118927973199334</v>
+        <v>-0.6983367509683305</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-2.843123845996033</v>
+        <v>-2.853553481694185</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-21 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-21 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>14.17322834645668</v>
+        <v>14.1857506361323</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.799749971587673</v>
+        <v>7.812659781163724</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.404881264991083</v>
+        <v>7.417888396408685</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.10656296902716</v>
+        <v>11.11954211142562</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.3776655634788</v>
+        <v>9.390776367853739</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.913202739289694</v>
+        <v>4.92624563558406</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.828469022017416</v>
+        <v>4.841535276317892</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.7898570518073456</v>
+        <v>0.8030380611025834</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.652095215327343</v>
+        <v>-1.63889647637258</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.311744209879073</v>
+        <v>-1.298339082226242</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-2.706973724672849</v>
+        <v>-2.693516430962632</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.902368987796123</v>
+        <v>-1.88881294144452</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.843123845996033</v>
+        <v>-2.853553481694185</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>118</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11.06588371368833</v>
+        <v>11.07840600336395</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.369564338012211</v>
+        <v>4.382474147588262</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.669610885652901</v>
+        <v>5.682618017070503</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.494779272497695</v>
+        <v>7.507758414896159</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.108900430306882</v>
+        <v>6.122011234681821</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.22077627604525</v>
+        <v>-1.207733379750884</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.305509993317528</v>
+        <v>-1.292443739017052</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.315066273454967</v>
+        <v>-4.301885264159729</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-6.918439040993199</v>
+        <v>-6.905240302038436</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-5.430944668982775</v>
+        <v>-5.417487375272557</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.854188630281406</v>
+        <v>-2.840736341561296</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.121900868344952</v>
+        <v>-4.108344821993349</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.177264281831384</v>
+        <v>-2.187693917529536</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>156</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.76297193620028</v>
+        <v>7.775494225875903</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.946270118107819</v>
+        <v>2.95917992768387</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.397555257665068</v>
+        <v>6.410562389082671</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.80985967232386</v>
+        <v>7.822838814722324</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.707335893149121</v>
+        <v>4.720446697524061</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.7644529383659844</v>
+        <v>-0.751410042071619</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.8491866556382632</v>
+        <v>-0.8361204013377872</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.880472618522333</v>
+        <v>-3.867291609227095</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.864549427781547</v>
+        <v>-5.851350688826784</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.150572048706913</v>
+        <v>-4.137166921054082</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.71429973199885</v>
+        <v>-3.700842438288632</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.756839651576506</v>
+        <v>-1.743387362856396</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.536068621495758</v>
+        <v>-1.522512575144155</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.6367296338574491</v>
+        <v>0.6262999981592969</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>201</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.710541779292512</v>
+        <v>6.723064068968135</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.098968166328255</v>
+        <v>5.111877975904306</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.689174086597333</v>
+        <v>7.702181218014935</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.321914781393886</v>
+        <v>7.33489392379235</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.793443815077936</v>
+        <v>4.806554619452875</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.608298688116982</v>
+        <v>1.621341584411347</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.523564970844703</v>
+        <v>1.536631225145179</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.9336681791805788</v>
+        <v>-0.920487169885341</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.487205378795707</v>
+        <v>-2.474006639840944</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.347280812579868</v>
+        <v>-1.333875684927037</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.054521699086493</v>
+        <v>-1.041064405376275</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.964936085124613</v>
+        <v>1.978388373844723</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.042193911990651</v>
+        <v>2.055749958342254</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.28196499551072</v>
+        <v>4.271535359812567</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.430804104032447</v>
+        <v>2.44332639370807</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.09195776379547</v>
+        <v>3.104867573371521</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.212240572350396</v>
+        <v>4.225247703767998</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.721281583745771</v>
+        <v>4.734260726144235</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.804072489885726</v>
+        <v>3.817183294260666</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.449999276086224</v>
+        <v>1.46304217238059</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.744053437601835</v>
+        <v>1.757119691902311</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2382814763311885</v>
+        <v>-0.2251004670359507</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.056857120089248</v>
+        <v>-1.043658381134485</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7706186687535421</v>
+        <v>-0.757213541100711</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-1.719490456936661</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.710526315789473</v>
+        <v>1.723978604509583</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.805423219996079</v>
+        <v>2.818979266347682</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.281265073069697</v>
+        <v>3.423502795362097</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.281209567113969</v>
+        <v>3.293731856789591</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.514706376684927</v>
+        <v>2.527616186260978</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.964908092623546</v>
+        <v>2.977915224041148</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.503611929456397</v>
+        <v>4.516591071854862</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.373641418609573</v>
+        <v>5.386752222984512</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.699252370409745</v>
+        <v>3.71229526670411</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.769448230602258</v>
+        <v>2.782514484902734</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.457194409285549</v>
+        <v>1.470375418580787</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5511241005680318</v>
+        <v>0.5643228395227951</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.8623813661500321</v>
+        <v>-0.8489762384972011</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.193895253847906</v>
+        <v>-2.180437960137688</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.03275153312218</v>
+        <v>-1.01929924440207</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.2371347010033347</v>
+        <v>0.2506907473549376</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3651085995245538</v>
+        <v>0.47642639758147</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.884136050499407</v>
+        <v>2.89665834017503</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.73022834142531</v>
+        <v>1.743138151001361</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.937190298444285</v>
+        <v>2.950197429861888</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.753942286887025</v>
+        <v>3.766921429285489</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.817351735430407</v>
+        <v>4.830462539805346</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.13996529786003</v>
+        <v>2.153008194154395</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.512897484477918</v>
+        <v>2.525963738778394</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.130382277916091</v>
+        <v>1.143563287211329</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.527048295623949</v>
+        <v>1.540247034578712</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2384086971842976</v>
+        <v>-0.2250035695314665</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.9008279253920364</v>
+        <v>-0.8873706316818186</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.6376118161015256</v>
+        <v>-0.6241595273814156</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.6002005231562677</v>
+        <v>-0.5866444768046648</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2218918669658834</v>
+        <v>-0.1320758746330526</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.586775583533338</v>
+        <v>2.599297873208961</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.9752019705690813</v>
+        <v>0.9881117801451325</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.25413005541634</v>
+        <v>3.267137186833942</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.097395665742205</v>
+        <v>4.110374808140669</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.341505644965935</v>
+        <v>5.354616449340874</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.252138313519382</v>
+        <v>2.265181209813747</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.989151476817518</v>
+        <v>2.002217731117995</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.8089556003176526</v>
+        <v>0.8221366096128904</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.747955714135351</v>
+        <v>0.7611544530901142</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.8151819486109346</v>
+        <v>-0.8017768209581035</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.089453989506055</v>
+        <v>-2.075996695795837</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.77973342447028</v>
+        <v>-1.863365424010922</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.102556397285859</v>
+        <v>-2.186431989063578</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.755054209539296</v>
+        <v>-1.684373824142426</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.3863353714449</v>
+        <v>2.398857661120523</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.623418052681501</v>
+        <v>1.636327862257552</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.784419218786461</v>
+        <v>2.797426350204063</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.366350146222786</v>
+        <v>3.379460950597725</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.825036779836601</v>
+        <v>1.838079676130967</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.7502040526633422</v>
+        <v>0.7632703069638183</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4244633695819786</v>
+        <v>0.4376443788772164</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.4851928108011734</v>
+        <v>-0.4719940718464102</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.325417005730088</v>
+        <v>-2.312011878077257</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.38872761434753</v>
+        <v>-2.375270320637313</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.561299592013782</v>
+        <v>-2.623777599682278</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.047252473105146</v>
+        <v>-3.10964121609716</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.005461508333696</v>
+        <v>-2.949804748158215</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6383111398332204</v>
+        <v>0.6508334295088432</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.7545992979272782</v>
+        <v>0.7675091075033293</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7916960340952741</v>
+        <v>0.8047031655128762</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1660096418647612</v>
+        <v>0.1789887842632254</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.787415640615478</v>
+        <v>1.800526444990417</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.436909414184278</v>
+        <v>1.449952310478643</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.05627936861824878</v>
+        <v>0.06934562291872481</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4109040301632518</v>
+        <v>-0.397723020868014</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.01186071980127</v>
+        <v>-0.9986619808465065</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.401942708284921</v>
+        <v>-2.388537580632089</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.008132025831145</v>
+        <v>-2.053281935436559</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.02323991797676</v>
+        <v>-2.068404687873716</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.384750456093087</v>
+        <v>-2.429938482570059</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.726916842587293</v>
+        <v>-2.6871705688324</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2557025732608196</v>
+        <v>0.2682248629364423</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.01222842801959</v>
+        <v>-0.9993186184435388</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.664829093379069</v>
+        <v>-1.651821961961467</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.964129225376375</v>
+        <v>-1.951150082977911</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3547841174245008</v>
+        <v>-0.3416733130495615</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.8702800433332456</v>
+        <v>-0.9034058126240936</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.212967328963224</v>
+        <v>-1.199901074662748</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.110073341674209</v>
+        <v>-2.096892332378971</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.085088705070611</v>
+        <v>-2.071889966115847</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.107182935670338</v>
+        <v>-3.093777808017506</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.094237063743414</v>
+        <v>-3.1265099207059</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.755647045732736</v>
+        <v>-2.788226058297489</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.129790991080192</v>
+        <v>-3.162345610326035</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.351567085241683</v>
+        <v>-3.32153377726069</v>
       </c>
     </row>
     <row r="17">
@@ -4480,101 +4480,101 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.6715759720318388</v>
+        <v>-0.6590536823562161</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.945767668666811</v>
+        <v>-1.93285785909076</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.126061476477979</v>
+        <v>-1.113054345060377</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.13076111040219</v>
+        <v>-1.117781968003726</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4853613488391417</v>
+        <v>-0.5089730055798469</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.8268230007360557</v>
+        <v>-0.8500959611491652</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.280871265821858</v>
+        <v>-1.303895869113255</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.748054664603359</v>
+        <v>-1.734873655308121</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.60621479419337</v>
+        <v>-1.593016055238607</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.555381042149193</v>
+        <v>-2.578161355963324</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.046851856020176</v>
+        <v>-2.070087086288353</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.314479843363031</v>
+        <v>-2.337540445161132</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.426985614107672</v>
+        <v>-2.45017569792924</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.022422159622707</v>
+        <v>-3.001253239563432</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.000389</t>
+          <t>X &lt; -0.0003892</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.9426361811725457</v>
+        <v>-0.9576664313895122</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.53816701338814</v>
+        <v>-1.525257203812089</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.476873684179601</v>
+        <v>-1.49222110193611</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.997036500739334</v>
+        <v>-1.012614121854213</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.596318674029817</v>
+        <v>-0.6122826716078791</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7520858841982943</v>
+        <v>-0.7678906155955829</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.504991976322941</v>
+        <v>-1.52043073195037</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.158232055080042</v>
+        <v>-2.173471577605454</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.083427168398423</v>
+        <v>-2.098737064968532</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.743896017970734</v>
+        <v>-2.75911662996031</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.490116428288417</v>
+        <v>-2.505546506150594</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.695632041981789</v>
+        <v>-2.710953738805351</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.441573373154363</v>
+        <v>-2.457169316252504</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.80852443034172</v>
+        <v>-2.793997652907592</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.728361812559214</v>
+        <v>-1.738675814609927</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.966335661224662</v>
+        <v>-1.976890602446062</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.157538297428481</v>
+        <v>-2.168098181923689</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.048762252544122</v>
+        <v>-2.05935106746756</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.48153835253305</v>
+        <v>-1.492504389244061</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.250209851727767</v>
+        <v>-1.261224844041521</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.032885628145898</v>
+        <v>-2.043573300265656</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.295706744817402</v>
+        <v>-2.306382602469711</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.377995331471361</v>
+        <v>-2.388654618907239</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.752365645981754</v>
+        <v>-2.763044205467956</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.34531007186996</v>
+        <v>-2.356223809440451</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.557904258611259</v>
+        <v>-2.568722365406579</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.094138003094557</v>
+        <v>-2.105263157894747</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.227137297460814</v>
+        <v>-2.216837256742664</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.551523092580467</v>
+        <v>-1.558985861840746</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.494097131446708</v>
+        <v>-1.501835247617016</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.043478440242147</v>
+        <v>-1.051459295553848</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.8922208273990861</v>
+        <v>-0.9002461652361831</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.5448411750656774</v>
+        <v>-0.5530911595108421</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4226398163719693</v>
+        <v>-0.4308972215588014</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.036803916426251</v>
+        <v>-1.044838148396074</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.404161051301664</v>
+        <v>-1.412128099775622</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.483366306440949</v>
+        <v>-1.491316783338341</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.879084182496712</v>
+        <v>-1.887015497674319</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.78667652777991</v>
+        <v>-1.794681118972534</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.927897735523821</v>
+        <v>-1.935846597868817</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.971844727618866</v>
+        <v>-1.979846595741876</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.818891667917697</v>
+        <v>-1.811417384353035</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2832</v>
+        <v>2833</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.175336386993813</v>
+        <v>-1.180845756465487</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.643689851598985</v>
+        <v>-1.649219874037549</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.492494076281552</v>
+        <v>-1.498125266440425</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.449148970921236</v>
+        <v>-1.454784136836615</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.053772059088708</v>
+        <v>-1.059610683518542</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8782124183226543</v>
+        <v>-0.8840827196228602</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.578045679671646</v>
+        <v>-1.583682698195865</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.56844356230723</v>
+        <v>-1.574140355174116</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.716297843858484</v>
+        <v>-1.721952954777898</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.842337265154782</v>
+        <v>-1.848047862460234</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.710501061533513</v>
+        <v>-1.716284917764966</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.833292250964881</v>
+        <v>-1.839032458501485</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.775463301412849</v>
+        <v>-1.781275219227908</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.824156937198616</v>
+        <v>-1.818557767912736</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.333686605084196</v>
+        <v>-1.337872268287455</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.654031541017368</v>
+        <v>-1.65825697495395</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.672159162163766</v>
+        <v>-1.676415992013347</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.720837448301317</v>
+        <v>-1.72506941739644</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.260682022857019</v>
+        <v>-1.265114503864474</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.305632962530296</v>
+        <v>-1.310027087440382</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.798450158093253</v>
+        <v>-1.80269309565918</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.757153894024817</v>
+        <v>-1.761454184240726</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.669642358652411</v>
+        <v>-1.67397927176971</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.879677805335611</v>
+        <v>-1.884023732765137</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.902787743495722</v>
+        <v>-1.907146837253585</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.080084712526478</v>
+        <v>-2.084385270225987</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.925014976332577</v>
+        <v>-1.929406227939445</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.919801761256622</v>
+        <v>-1.915306749744595</v>
       </c>
     </row>
     <row r="23">
@@ -4792,101 +4792,101 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.9661319332923597</v>
+        <v>-0.9695033223295439</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.11118477268041</v>
+        <v>-1.114626035970907</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.427944857121851</v>
+        <v>-1.431317952797663</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.466600947558632</v>
+        <v>-1.46995494086859</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.278144489921615</v>
+        <v>-1.281596348990874</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.365860183778175</v>
+        <v>-1.369266081614406</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.71234204738716</v>
+        <v>-1.715648783956404</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.606556058891485</v>
+        <v>-1.609930217398933</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.589128488271527</v>
+        <v>-1.592514287133241</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.741965803467004</v>
+        <v>-1.745366021675089</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.620401677098016</v>
+        <v>-1.623855893480311</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.847734309034621</v>
+        <v>-1.851117763065901</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.817571984448485</v>
+        <v>-1.820996341120185</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.736733334401052</v>
+        <v>-1.733126989635608</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.08296</t>
+          <t>X &lt; 0.08295</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.8017642984388687</v>
+        <v>-0.8044454422990626</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.103246188618613</v>
+        <v>-1.105929719950048</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.276448199382251</v>
+        <v>-1.279104232308484</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.483879568411851</v>
+        <v>-1.486468794555847</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.21143605655066</v>
+        <v>-1.214136975575506</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.399056990766141</v>
+        <v>-1.401687599565669</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.556525294011387</v>
+        <v>-1.559115732465116</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.742712579818892</v>
+        <v>-1.745275694107725</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.640509926537689</v>
+        <v>-1.643108066669079</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.560374635500651</v>
+        <v>-1.563045377601959</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.512984768807229</v>
+        <v>-1.515682465518047</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.728080531908283</v>
+        <v>-1.730714386182228</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.68936970482342</v>
+        <v>-1.692040017398881</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.718746156349582</v>
+        <v>-1.715799886013215</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3505</v>
+        <v>3506</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.5889471320348818</v>
+        <v>-0.5911746267264562</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7072297324349677</v>
+        <v>-0.7094983714662817</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.00158712441246</v>
+        <v>-1.003791336047279</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9983615043183676</v>
+        <v>-1.000561902876349</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8670697808581451</v>
+        <v>-0.8693333659402143</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.038161580990078</v>
+        <v>-1.040364115886248</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.250010205664552</v>
+        <v>-1.252157538126419</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.331706469642256</v>
+        <v>-1.333853141847847</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.377369940602065</v>
+        <v>-1.379507616869795</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.243212950125248</v>
+        <v>-1.245429029316192</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.261298533273596</v>
+        <v>-1.263520095010179</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.467857176965282</v>
+        <v>-1.47001952962539</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.501695312735684</v>
+        <v>-1.503868544524082</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.493011761219179</v>
+        <v>-1.490583878564856</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3618</v>
+        <v>3619</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.5518244397362722</v>
+        <v>-0.55360325520396</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.4686482968105921</v>
+        <v>-0.4705102756224093</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9038486750422479</v>
+        <v>-0.9056062907223605</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9793298224885731</v>
+        <v>-0.981062804004317</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8137559182652723</v>
+        <v>-0.8155553379267104</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.9150745175589847</v>
+        <v>-0.916836013949208</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.012581881102456</v>
+        <v>-1.014320579537966</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.133826328829677</v>
+        <v>-1.135549787830101</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.262717824845893</v>
+        <v>-1.26440893301087</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.13162798890145</v>
+        <v>-1.133387647608785</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.10027470703762</v>
+        <v>-1.102051573346479</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.216394829363722</v>
+        <v>-1.218139343822124</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.317492871005122</v>
+        <v>-1.319225990642103</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.32886971980161</v>
+        <v>-1.326888657157014</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4246580945248581</v>
+        <v>-0.4261215099864089</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3291452306749036</v>
+        <v>-0.3306835314434267</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.9246118225665185</v>
+        <v>-0.9260027746794677</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9681755039366422</v>
+        <v>-0.9695515905713137</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6853483456889649</v>
+        <v>-0.6868174553706368</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6961596497337155</v>
+        <v>-0.6976176805869514</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8202059485090132</v>
+        <v>-0.821633946173371</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.003708288191369</v>
+        <v>-1.005101771795054</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.07705098115548</v>
+        <v>-1.078427335822688</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.9699592330281135</v>
+        <v>-0.9713908554395658</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9712902271359027</v>
+        <v>-0.9727284658978022</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.164525740750058</v>
+        <v>-1.165911677622084</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.246483992288496</v>
+        <v>-1.247861330403992</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.143589893833344</v>
+        <v>-1.141963185198229</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.373343508516534</v>
+        <v>-0.3745442559161347</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.3642321649972047</v>
+        <v>-0.3654758396898288</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.7976408505745098</v>
+        <v>-0.798780779164602</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.9695220775375972</v>
+        <v>-0.970614109165389</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.7029340372895376</v>
+        <v>-0.7041102952986122</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6812818900050672</v>
+        <v>-0.6824571125861354</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7254117231057506</v>
+        <v>-0.726578044959993</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.8881175681197817</v>
+        <v>-0.8892532051797204</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.9347932509945025</v>
+        <v>-0.9359187153473201</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.8994145472854242</v>
+        <v>-0.9005711072611149</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.9839739887341139</v>
+        <v>-0.9851139569846552</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.067051362739079</v>
+        <v>-1.06816917377499</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.182107303201555</v>
+        <v>-1.183205817453882</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.023431910025018</v>
+        <v>-1.022075844404128</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3854</v>
+        <v>3855</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1789826698350083</v>
+        <v>-0.1799853169872989</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1474330402616602</v>
+        <v>-0.1484765740765894</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.502467961892421</v>
+        <v>-0.5034280867287961</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6429194326291636</v>
+        <v>-0.6438411202629197</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3908341221837119</v>
+        <v>-0.391832327798447</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.441782341226201</v>
+        <v>-0.4427619208426066</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4865862930379024</v>
+        <v>-0.4875564846744425</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5770316725943374</v>
+        <v>-0.5779883199238043</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6498000241231026</v>
+        <v>-0.6507395555731676</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6304141350808834</v>
+        <v>-0.631376261855813</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.691158324102453</v>
+        <v>-0.692109336242936</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.797961047469677</v>
+        <v>-0.7988841951227243</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8666083800510833</v>
+        <v>-0.8675226826023987</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7580915974972555</v>
+        <v>-0.7570183695948671</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3915</v>
+        <v>3916</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.001470030095525487</v>
+        <v>0.0006314370146398574</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.03300691072696083</v>
+        <v>0.03213412894763934</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2207160957056189</v>
+        <v>-0.2215310077166066</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4333217746792428</v>
+        <v>-0.4340808660384212</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2444401595443537</v>
+        <v>-0.2452563891981328</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2899338301481791</v>
+        <v>-0.2907341226801066</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2843257134188306</v>
+        <v>-0.2851292054319856</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3805805187832547</v>
+        <v>-0.3813673685858703</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4020952153273356</v>
+        <v>-0.4028779679745753</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4727303700997396</v>
+        <v>-0.473509150253463</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.4591067371427684</v>
+        <v>-0.45989269312863</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5636515104690361</v>
+        <v>-0.5644106478919326</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.612179776258607</v>
+        <v>-0.6129336849678779</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6035690202343105</v>
+        <v>-0.602714433102328</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3960</v>
+        <v>3961</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.03937338187621719</v>
+        <v>-0.0400504039616365</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.09941908394560528</v>
+        <v>0.09868569417176332</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.004791241634336529</v>
+        <v>-0.00550392124344512</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2638340562817092</v>
+        <v>-0.2644801451728185</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.05796053881397256</v>
+        <v>-0.05866587755828334</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.0743164619391834</v>
+        <v>-0.07501412758046655</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.0948867584092028</v>
+        <v>-0.09558069910453071</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1448738753592878</v>
+        <v>-0.1455616964207991</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1667772545995447</v>
+        <v>-0.1674607008520752</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2714289919654718</v>
+        <v>-0.2720975641814505</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2350008325636992</v>
+        <v>-0.2356816320582098</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3379111125066174</v>
+        <v>-0.3385658406995233</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3906054841113971</v>
+        <v>-0.3912527866405497</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4297039325761176</v>
+        <v>-0.4290214371166954</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4003</v>
+        <v>4004</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.02150191883385588</v>
+        <v>0.02095103443951274</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1415634092915212</v>
+        <v>0.1409656054854835</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.01557570703539568</v>
+        <v>-0.01613876364586986</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2704498345991553</v>
+        <v>-0.2709483149392469</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.0974804271208356</v>
+        <v>-0.09802787549823222</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.08555068878310834</v>
+        <v>-0.08609828503504247</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.05693651176716941</v>
+        <v>-0.05749239757889058</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.06150120164619466</v>
+        <v>-0.0620610957671488</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.05885312807327381</v>
+        <v>-0.05941459631699075</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.171477771384545</v>
+        <v>-0.1720202912367981</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1875385916580825</v>
+        <v>-0.1880795169906477</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.1890878029257692</v>
+        <v>-0.189628257924042</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.2456923311194714</v>
+        <v>-0.2462233213268092</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2316895645642418</v>
+        <v>-0.2311758593165578</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4033</v>
+        <v>4034</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.002854314490960519</v>
+        <v>0.002404947968237536</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1100684129320726</v>
+        <v>0.1095785486707257</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.0735700561902064</v>
+        <v>-0.07401813134456603</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2266643609847421</v>
+        <v>-0.2270736862287492</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.05896411065706531</v>
+        <v>-0.05941973829092007</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.02015887558639662</v>
+        <v>-0.02062178035807705</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.01712268000992623</v>
+        <v>-0.01758728881804217</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.04987225412646978</v>
+        <v>-0.05033299028826832</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.02292943311549323</v>
+        <v>-0.02339759050973811</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.09148399779324734</v>
+        <v>-0.09194270495319756</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.08415056171092772</v>
+        <v>-0.08461307274047414</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.03584070009428331</v>
+        <v>-0.0363151156453867</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.04553304568501915</v>
+        <v>-0.04600890533194502</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.004931787620485295</v>
+        <v>-0.004555677317100049</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4058</v>
+        <v>4059</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.02475740642957902</v>
+        <v>-0.02512035273473856</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.02275219458989852</v>
+        <v>0.02236606603582203</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.0639012836636681</v>
+        <v>-0.06426908574879775</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1660876841544692</v>
+        <v>-0.1664296378049173</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.002713094008299777</v>
+        <v>-0.003099176464296249</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.06229041174184857</v>
+        <v>0.06189025487756084</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.008993638323474329</v>
+        <v>-0.009377051229954247</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.01980736514054371</v>
+        <v>-0.02019159976546092</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.006601736256641288</v>
+        <v>0.006210385269717733</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.042137401128997</v>
+        <v>-0.04252294824127745</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.08534639853924375</v>
+        <v>-0.08572294429174576</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.03712258703184546</v>
+        <v>-0.03751095247370273</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-7.074403446694078e-05</v>
+        <v>-0.0004713979305677185</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.04183003698643262</v>
+        <v>0.04212807252395834</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.0344219267673509</v>
+        <v>-0.03473207750108998</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.03106246721734607</v>
+        <v>0.03072635694989856</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1057557927695996</v>
+        <v>-0.1060609777609471</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1335844121584273</v>
+        <v>-0.1338821468945994</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.0270480203557355</v>
+        <v>0.02670752778097807</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1174676887775732</v>
+        <v>0.1171066971284418</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.07064822646076863</v>
+        <v>0.07029802100420568</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.08257413864208019</v>
+        <v>0.08221800065987139</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.05963384991974152</v>
+        <v>0.05928279533610947</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.03228530972670285</v>
+        <v>0.03193561161795344</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.01153940672197251</v>
+        <v>-0.01187977433823306</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.01211432542458368</v>
+        <v>0.01176820024618763</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.09646244661812631</v>
+        <v>0.09609289527681852</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1146572045685232</v>
+        <v>0.1148952474907432</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_21.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_21.xlsx
@@ -575,46 +575,46 @@
         <v>34</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.389633695057093</v>
+        <v>3.360567976008092</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.080257595525737</v>
+        <v>-4.081472122135253</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.391270309327361</v>
+        <v>1.391129867508873</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.412489543312745</v>
+        <v>-1.412989493017406</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.94979570818591</v>
+        <v>-1.901369843226789</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-16.33004861196899</v>
+        <v>-16.30622661996728</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-16.41858709407771</v>
+        <v>-16.37073713564391</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-16.88892311139553</v>
+        <v>-16.83981845516244</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-19.8914613431497</v>
+        <v>-19.81836426782768</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-17.80721876700331</v>
+        <v>-17.70802027538473</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-12.13818626024779</v>
+        <v>-12.03837900533166</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-12.10689765731771</v>
+        <v>-11.98328003426632</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-9.589491274153474</v>
+        <v>-9.440845947876525</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.5426291119462832</v>
+        <v>-0.3706303523809638</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>38</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.47388937642161</v>
+        <v>-2.503004204766377</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.456331485355243</v>
+        <v>-1.45752559867006</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.646798647932663</v>
+        <v>8.64671313289324</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.778823177612338</v>
+        <v>8.778392578819172</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.3670480540494268</v>
+        <v>0.4154858181676246</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.6644312242594452</v>
+        <v>0.6883420957581308</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5800620326748245</v>
+        <v>0.6279890160420933</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.513732983918615</v>
+        <v>-2.464573165378077</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.57518407236978</v>
+        <v>-2.502031883379196</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.832917458377572</v>
+        <v>1.932166138011127</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.628749946362213</v>
+        <v>1.728583199064154</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.663420444086853</v>
+        <v>1.787055198768819</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.505602395208975</v>
+        <v>6.654257825837249</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.36449163108778</v>
+        <v>9.53649039065683</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>45</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.063625632690716</v>
+        <v>3.034562327746904</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.53642042984134</v>
+        <v>12.53534314287938</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.14533954590578</v>
+        <v>12.14528372307237</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.628417811292387</v>
+        <v>5.627967840820375</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.093119085820355</v>
+        <v>5.141584377564065</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.827173446349718</v>
+        <v>9.851134638441579</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9.745122302466612</v>
+        <v>9.793092409413134</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>9.281336694968125</v>
+        <v>9.330543927662525</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.222852083511484</v>
+        <v>9.296043128649039</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.375979528106384</v>
+        <v>8.475244546345564</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.173475069539521</v>
+        <v>8.273320557955316</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>14.87310406636919</v>
+        <v>14.99675606159884</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>14.4567768620897</v>
+        <v>14.60543723711556</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>16.90835128021057</v>
+        <v>17.08035003977623</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>63</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-11.17487146127809</v>
+        <v>-11.2040636461025</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.288897304898484</v>
+        <v>-3.290105488637373</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.849590607860982</v>
+        <v>-6.849791705287174</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.554768619364964</v>
+        <v>-3.555282425936312</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.658590152746342</v>
+        <v>0.7070253605961909</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.9559588447389231</v>
+        <v>0.9798704689760029</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.456161843142517</v>
+        <v>2.504095306837229</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.990598642066935</v>
+        <v>2.039774254786657</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.515580358649423</v>
+        <v>3.588749852045538</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.081655235856701</v>
+        <v>1.180897547633982</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.880899537830658</v>
+        <v>-3.781081434209398</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.9118126249060623</v>
+        <v>1.035443789180526</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.252690428397557</v>
+        <v>5.401343626265657</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>-0.6974277380005347</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>91</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.740702934656362</v>
+        <v>5.71167279899737</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.8498376824701595</v>
+        <v>0.8486650528512385</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6397032366278879</v>
+        <v>-0.6398567489857356</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.874142757448652</v>
+        <v>3.873683377649762</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.916214455646376</v>
+        <v>9.964708446211539</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>10.21601147982706</v>
+        <v>10.239977530495</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.746631142175517</v>
+        <v>5.794579396246547</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.379162977241471</v>
+        <v>6.428355957250645</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.222566205515299</v>
+        <v>5.295739123404431</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.113877091381354</v>
+        <v>-1.014645552230164</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.514762703503983</v>
+        <v>-3.414947756177973</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-8.973119477782518</v>
+        <v>-8.849505875993842</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.198303699557208</v>
+        <v>-7.04966124578683</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-8.073333701474901</v>
+        <v>-7.901334941908239</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>82</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.172500765998485</v>
+        <v>1.143434176678973</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.648283539825144</v>
+        <v>-1.649478747154795</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.821035463533214</v>
+        <v>2.820911856545038</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5189380611662742</v>
+        <v>0.5184553102886227</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.415144680548977</v>
+        <v>2.463586232703491</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.588336641967715</v>
+        <v>-4.564460804833985</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.412288066698366</v>
+        <v>1.460210868153091</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.2709922309348158</v>
+        <v>-0.2218319537331084</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.757586808394294</v>
+        <v>5.830758857009869</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.473858595399868</v>
+        <v>2.573095944311163</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.707103497664562</v>
+        <v>4.806933245456293</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.086019670287776</v>
+        <v>1.209644702368252</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.210544824120468</v>
+        <v>-4.061902442806087</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.766445467756895</v>
+        <v>-2.594446708189679</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.576300588908452</v>
+        <v>1.515530465466156</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.693714666253584</v>
+        <v>-1.668810849425384</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.449676900459259</v>
+        <v>4.36956484489086</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.401912402684694</v>
+        <v>5.304424798142946</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.3134742933171</v>
+        <v>7.230993483593025</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.702567969832536</v>
+        <v>2.678071362057388</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1620349394104821</v>
+        <v>0.2036206114619432</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.3141600152114137</v>
+        <v>-0.2610935350537815</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.013833424793724</v>
+        <v>-1.908766161215247</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.881086253186695</v>
+        <v>-2.731951174276183</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.368964897110715</v>
+        <v>-6.159768126602039</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.335336972062223</v>
+        <v>-6.103407657221261</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-7.936037580232835</v>
+        <v>-8.112644795683906</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-7.244654184269926</v>
+        <v>-7.86588651936254</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>146</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.622264263015452</v>
+        <v>1.919399537544265</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.114943863952448</v>
+        <v>4.426533789391982</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9886716644508198</v>
+        <v>1.302413885918263</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.297955772296191</v>
+        <v>-1.981969516460772</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.203121009252271</v>
+        <v>-3.839637784177178</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1960963204506996</v>
+        <v>0.2197085951269173</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.991897209729821</v>
+        <v>-3.941842489113512</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.0386340093347</v>
+        <v>-0.9889303445541913</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.205833081916971</v>
+        <v>-5.129727523422154</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.11021829142615</v>
+        <v>-8.006215283158902</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.524078895592268</v>
+        <v>-3.422003031503074</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.545635343186717</v>
+        <v>-5.418601682444859</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.650717703349599</v>
+        <v>-6.5000289616464</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.794845066821381</v>
+        <v>-7.622846307254719</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.999072597597831</v>
+        <v>-5.047322495111324</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.040521728497687</v>
+        <v>-2.104450684046256</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.639089435889098</v>
+        <v>-5.690398302488497</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-8.256537088644201</v>
+        <v>-7.840012472747411</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.30395176978724</v>
+        <v>-3.321003829932536</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1985271614205999</v>
+        <v>1.054839407405922</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.177886407096963</v>
+        <v>-1.291650950410585</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.105751648788036</v>
+        <v>-2.427465005808827</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.71034712348969</v>
+        <v>-2.215280288448135</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.649278519254317</v>
+        <v>-2.334966182838983</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.021115424197006</v>
+        <v>-0.9125360312876438</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2672640977423058</v>
+        <v>-0.3984901770730289</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.2286993547253289</v>
+        <v>-0.3373201851425094</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.837826089820005</v>
+        <v>-1.915083750177097</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.22168736915107</v>
+        <v>-1.486964512012086</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-7.885596364207629</v>
+        <v>-8.124085293606726</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-11.2302087365097</v>
+        <v>-11.04237494600525</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-10.26161997724238</v>
+        <v>-10.07687088951218</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-8.697324181318955</v>
+        <v>-8.658959761810422</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-10.08771565472598</v>
+        <v>-10.06430055587934</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.150769288419845</v>
+        <v>-6.540141947263002</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.726934503388186</v>
+        <v>-8.687597444055719</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.260749029515182</v>
+        <v>-6.206108562022912</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.847062784938082</v>
+        <v>-5.774624591335289</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-7.319797323066304</v>
+        <v>-7.238866494252228</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.597655457630623</v>
+        <v>-5.682475164221067</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.017806310944323</v>
+        <v>-6.079576095153413</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.792070660717599</v>
+        <v>-5.832815226329203</v>
       </c>
     </row>
     <row r="16">
@@ -1092,153 +1092,153 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.082083751175205</v>
+        <v>-3.927141231924651</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.394547882430118</v>
+        <v>-5.201980940000837</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8608258397382826</v>
+        <v>0.999788939462519</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.942298180032907</v>
+        <v>1.931270990328827</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.132636894365</v>
+        <v>-1.071905146544665</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.6603293404174764</v>
+        <v>-0.7991690621952614</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.698016840300618</v>
+        <v>-1.802346947358259</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4056208410546276</v>
+        <v>-0.696453183704655</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1673633979260103</v>
+        <v>-0.1049131473176246</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.6868046906918579</v>
+        <v>-0.9278271904438071</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.830293092846823</v>
+        <v>1.382058226880872</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6750112944803988</v>
+        <v>-1.073751466145481</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1746791220474719</v>
+        <v>-0.2121463767200638</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.821807449948224</v>
+        <v>-2.164932979090686</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.007335</t>
+          <t>X ≈ -0.007336</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.126472121927257</v>
+        <v>-2.127701085936707</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.0202501006868161</v>
+        <v>-0.1108863386480294</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.977464406170675</v>
+        <v>-3.080944622498507</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.6197128108633478</v>
+        <v>-0.8898621397716013</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.015834852583829</v>
+        <v>-1.379509348724582</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4576563429289138</v>
+        <v>-0.8489446526163746</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.367222435627568</v>
+        <v>-2.713736528466491</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.879448066259748</v>
+        <v>-4.211482134009771</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-4.054598790817913</v>
+        <v>-4.506074693235441</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.456077177464344</v>
+        <v>-4.044749226813927</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.181611669057808</v>
+        <v>-4.506430010838699</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.147233516702542</v>
+        <v>-4.448502114274397</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.484051036682558</v>
+        <v>-2.891865963562687</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.997898719789418</v>
+        <v>-2.387003912112796</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.006555</t>
+          <t>X ≈ 0.006554</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>351</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5.909067546473871</v>
+        <v>-5.672406020615895</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.392541298439788</v>
+        <v>-4.266927094106705</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.768924790404505</v>
+        <v>-5.927686292080814</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.633001641118135</v>
+        <v>-7.790742270751032</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.176989199911702</v>
+        <v>-6.286308496681414</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.885313175974751</v>
+        <v>-4.018849535992203</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.824724389941714</v>
+        <v>-4.936311349472319</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.0125907545263</v>
+        <v>-3.125665779487647</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.928273765749871</v>
+        <v>-4.01746305918148</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.783890567777789</v>
+        <v>-2.850951753089902</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.564090301536559</v>
+        <v>-1.630590776124571</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.814612434081461</v>
+        <v>-1.857695771228251</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.2404612930928067</v>
+        <v>-0.2591707827704752</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.8399752118345063</v>
+        <v>1.011973971401169</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>326</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3336767667306049</v>
+        <v>-0.3628725610832362</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.736118735297524</v>
+        <v>1.734931948852868</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>6.556071276922857</v>
+        <v>6.555917886918536</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6.993044886768885</v>
+        <v>6.992550394390882</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5.841258401157781</v>
+        <v>5.889804320923552</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.218387032019933</v>
+        <v>5.242344440969546</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.747173605269033</v>
+        <v>5.795185284259354</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.666608028967055</v>
+        <v>4.715855591360771</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4.60562587244425</v>
+        <v>4.678882982223946</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.062455542372135</v>
+        <v>4.161802867666708</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.017263586565932</v>
+        <v>2.117171622584607</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.358390205178843</v>
+        <v>2.482086826207087</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.129245310711312</v>
+        <v>-0.9805557629334842</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.936981137061295</v>
+        <v>1.108979896627957</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>297</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.064538514920187</v>
+        <v>2.035342720567556</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.913650945147033</v>
+        <v>-2.914837731591689</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.328624350104022</v>
+        <v>-5.328777740108343</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-6.208500216616713</v>
+        <v>-6.208994708994716</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-5.399988422911058</v>
+        <v>-5.351442503145286</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.765914056575632</v>
+        <v>-4.741956647626019</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-6.197425762643185</v>
+        <v>-6.149414083652864</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.960790702726221</v>
+        <v>-2.911543140332505</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.695173532649633</v>
+        <v>-3.621916422869937</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.514789298676469</v>
+        <v>-1.415441973381895</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.046089783535976</v>
+        <v>-0.9461817475173007</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.011711631180653</v>
+        <v>-0.888015010152408</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.08506113769272616</v>
+        <v>0.06362841008510145</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>-1.707528748101552</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.406841956460276</v>
+        <v>-3.672902522561408</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.777287308783315</v>
+        <v>-1.535149375159065</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.023910545390258</v>
+        <v>-3.789352479752942</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-5.282574290690782</v>
+        <v>-5.519933554817285</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.969011991934678</v>
+        <v>-4.148717579490125</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-6.912378703040282</v>
+        <v>-6.666629735089863</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.682274247491577</v>
+        <v>-4.401704428966383</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.223416965352399</v>
+        <v>-3.937304631210232</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.043658381134485</v>
+        <v>-0.7184632868586576</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.356540140427299</v>
+        <v>-2.007408146743408</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.413093150539353</v>
+        <v>-4.072013710558572</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.304640924109947</v>
+        <v>-4.944079531333209</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.872939925571508</v>
+        <v>-3.478772341617976</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.184241312382007</v>
+        <v>-2.76461120053284</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>5.29686174724349</v>
+        <v>5.500937898869985</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>8.130120098624111</v>
+        <v>7.785164128631259</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.735348713868945</v>
+        <v>2.419050449708756</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.865573857457363</v>
+        <v>3.10142067876874</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.561604584527153</v>
+        <v>-1.255231777100306</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.375341666003237</v>
+        <v>-2.639904821817225</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2378298030471271</v>
+        <v>-0.4906161596614709</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.9617682198327415</v>
+        <v>0.7010096434910906</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.2103250478010921</v>
+        <v>-0.4409353413363064</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6064228225356558</v>
+        <v>0.3926946413845585</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.179499442053242</v>
+        <v>2.950985133074994</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.102766483297394</v>
+        <v>1.904179494749215</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.01594896331744167</v>
+        <v>-0.1484369953503943</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.352795724655088</v>
+        <v>1.205580242355573</v>
       </c>
     </row>
     <row r="23">
@@ -1459,98 +1459,98 @@
         <v>158</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.582375108706081</v>
+        <v>2.55317931435345</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.9275451615729366</v>
+        <v>-0.9287319480175924</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.842240415697411</v>
+        <v>1.84208702569309</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.82500279514457</v>
+        <v>-1.825497287522573</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1683532213799595</v>
+        <v>0.2168991411457313</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.065918318605178</v>
+        <v>-2.041960909655565</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.646839676558919</v>
+        <v>1.69485135554924</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.516431498873381</v>
+        <v>-4.467183936479664</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.678679478180968</v>
+        <v>-2.605422368401271</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.167604257134812</v>
+        <v>2.266951582429385</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6970803140645003</v>
+        <v>0.7969883500831756</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.7314584664198875</v>
+        <v>0.8551550874481322</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.9442190055114352</v>
+        <v>1.092908553289263</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.36169091388232</v>
+        <v>-1.189692154315658</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.0899</t>
+          <t>X ≈ 0.08988</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>119</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>5.502277246776579</v>
+        <v>5.473081452423948</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>10.61378022934299</v>
+        <v>10.61259344289834</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>6.857664306772833</v>
+        <v>6.857510916768511</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>12.87024239153761</v>
+        <v>12.86974789915961</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>8.970608300626836</v>
+        <v>9.019154220392608</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>9.26798233026188</v>
+        <v>9.291939739211493</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.502599702088197</v>
+        <v>7.550611381078518</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>10.39687559611658</v>
+        <v>10.4461231585103</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.134212767324904</v>
+        <v>6.2074698771046</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.805302374356337</v>
+        <v>7.904649699650911</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.91992894718863</v>
+        <v>6.019836983207306</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.954307099543954</v>
+        <v>6.078003720572198</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.853483977322931</v>
+        <v>4.002173525100758</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.919555762003299</v>
+        <v>5.091554521569961</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>113</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6164291022090183</v>
+        <v>0.5872333078563869</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.969844779056736</v>
+        <v>6.96865799261208</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.150294633239753</v>
+        <v>2.150141243235431</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.37434747980911</v>
+        <v>-0.374841972187113</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.8572744715200287</v>
+        <v>0.9058203912858005</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.924560005579842</v>
+        <v>2.948517414529455</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.379672655163226</v>
+        <v>6.427684334153547</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.02764825916411</v>
+        <v>5.076895821557827</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.311798846004109</v>
+        <v>2.385055955783805</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.346835801886691</v>
+        <v>2.446183127181264</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.912046148051225</v>
+        <v>4.0119541840699</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.601291557043766</v>
+        <v>6.72498817807201</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.411229199305573</v>
+        <v>4.559918747083401</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.752009097319672</v>
+        <v>3.924007856886334</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>91</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.661941112322751</v>
+        <v>4.632745317970119</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.248557217061091</v>
+        <v>5.247370430616435</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.739620761100539</v>
+        <v>-1.739774151104861</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5104945186110115</v>
+        <v>-0.5109890109890145</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.445721422798719</v>
+        <v>4.494267342564491</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>8.039798749137169</v>
+        <v>8.063756158086782</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.856187290969906</v>
+        <v>6.904198969960227</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.191316449381034</v>
+        <v>4.240564011774751</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.328136490660448</v>
+        <v>6.401393600440144</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.478217694330588</v>
+        <v>5.577565019625162</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.174615437169365</v>
+        <v>4.27452347318804</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.9122902928212042</v>
+        <v>1.035986913849449</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.591040538409018</v>
+        <v>1.739730086186846</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.212380584239952</v>
+        <v>6.384379343806614</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>75</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.185750636132354</v>
+        <v>2.156554841779723</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.092102123598181</v>
+        <v>-2.093288910042837</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.512973101642459</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.023315031431522</v>
+        <v>-1.023809523809526</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.561604584527217</v>
+        <v>-1.513058664761445</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.06910277844116308</v>
+        <v>0.09306018739077615</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.984392419175066</v>
+        <v>4.032404098165387</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.850657108721549</v>
+        <v>4.899904671115266</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.123008285532222</v>
+        <v>6.196265395311919</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.606422822535656</v>
+        <v>2.705770147830229</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.598278335724615</v>
+        <v>-1.49837029970594</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.769433149964165</v>
+        <v>3.89312977099241</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.0159489633173</v>
+        <v>2.164638511095127</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.908351280210574</v>
+        <v>5.080350039777237</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>70</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10.3762268266085</v>
+        <v>10.34703103225587</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>11.62218359068753</v>
+        <v>11.62099680424287</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>15.51312649164678</v>
+        <v>15.51297310164246</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>17.07192306380657</v>
+        <v>17.07142857142857</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>16.53363351071088</v>
+        <v>16.58217943047665</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>12.54529325463172</v>
+        <v>12.56925066358133</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>12.46058289536548</v>
+        <v>12.5085945743558</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>16.27922853729306</v>
+        <v>16.32847609968677</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>14.78967495219881</v>
+        <v>14.8629320619785</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>13.93975615586899</v>
+        <v>14.03910348116356</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>15.16362642618023</v>
+        <v>15.2635344621989</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>13.76943314996421</v>
+        <v>13.89312977099245</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>16.20642515379356</v>
+        <v>16.35511470157139</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>13.57501794687725</v>
+        <v>13.74701670644391</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>11.45351019897385</v>
+        <v>10.8232215084464</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>11.48166836820515</v>
+        <v>10.90671108995716</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>17.64427403263034</v>
+        <v>17.17963976830913</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>12.8564663893335</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>9.039488311647695</v>
+        <v>8.486941335238505</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.336862341282682</v>
+        <v>8.759726854057533</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12.53084050660672</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>12.06377186282003</v>
+        <v>11.566571337782</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>15.28147823088737</v>
+        <v>14.86293206197855</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.513526647672222</v>
+        <v>10.70577014783018</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>14.22685827629728</v>
+        <v>13.83496303362753</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>14.26123642865264</v>
+        <v>13.89312977099237</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>15.48042983763432</v>
+        <v>16.83130517776187</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>9.148788438680519</v>
+        <v>8.747016706443908</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.592027141645467</v>
+        <v>-2.510111824887048</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.907897876401762</v>
+        <v>6.776276307348475</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>18.84645982498021</v>
+        <v>19.42601657990336</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>14.53224052412403</v>
+        <v>15.20807453416148</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>16.21617319325053</v>
+        <v>16.89273843668793</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>18.73576944510793</v>
+        <v>19.33943699898495</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16.42883686361951</v>
+        <v>17.10486786628132</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>20.40621266427711</v>
+        <v>20.98686119285448</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>20.34523050775441</v>
+        <v>20.94988858371769</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>17.27308948920239</v>
+        <v>15.77823391594623</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>19.29061055316441</v>
+        <v>19.92191955536654</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>19.32498870551961</v>
+        <v>19.98008629273144</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>18.90483785220627</v>
+        <v>17.4110153226894</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>14.68612905798836</v>
+        <v>15.48614714122652</v>
       </c>
     </row>
     <row r="31">
@@ -1875,150 +1875,150 @@
         <v>43</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.658618853186582</v>
+        <v>5.62942305883395</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.047432760122753</v>
+        <v>4.046245973678097</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.9985014153300042</v>
+        <v>-0.9986548053343256</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.8682762717416068</v>
+        <v>-0.8687707641196099</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.732147220186164</v>
+        <v>-3.683601300420392</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.109191795202214</v>
+        <v>-1.085234386252601</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.457260636229265</v>
+        <v>3.505272315219585</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.64135478314023</v>
+        <v>7.690602345533947</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.905954021966338</v>
+        <v>9.979211131746034</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.056035225636435</v>
+        <v>9.155382550931009</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.200171276678596</v>
+        <v>4.300079312697271</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>13.53687501042928</v>
+        <v>13.66057163145752</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>13.11672415711583</v>
+        <v>13.26541370489365</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>17.99362259804004</v>
+        <v>18.1656213576067</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.2011</t>
+          <t>X ≈ 0.201</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>30</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.480916030534402</v>
+        <v>-2.510111824887034</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.092102123598231</v>
+        <v>-4.093288910042887</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-7.820206841686556</v>
+        <v>-7.820360231690877</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>5.642857142857139</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.10506208213949</v>
+        <v>5.153608001905262</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.735769445107863</v>
+        <v>8.759726854057476</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.317725752508409</v>
+        <v>5.365737431498729</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.517323775388292</v>
+        <v>1.566571337782008</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.789674952198801</v>
+        <v>4.862932061978498</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.73505499760876</v>
+        <v>13.83496303362743</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>20.43609981663074</v>
+        <v>20.55979643765898</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>26.68261562998406</v>
+        <v>26.83130517776188</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>30.24168461354392</v>
+        <v>30.41368337311058</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.2149</t>
+          <t>X ≈ 0.2148</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>25</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.480916030534296</v>
+        <v>-4.510111824886927</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-14.09210212359815</v>
+        <v>-14.09328891004281</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.513126491646808</v>
+        <v>1.512973101642487</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>9.643351635235142</v>
+        <v>9.642857142857139</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9.105062082139362</v>
+        <v>9.153608001905134</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>13.40243611177453</v>
+        <v>13.42639352072415</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.317725752508338</v>
+        <v>1.365737431498658</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.850657108721656</v>
+        <v>4.899904671115372</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.78967495219888</v>
+        <v>4.862932061978576</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.939756155868992</v>
+        <v>8.039103481163565</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2649450023911939</v>
+        <v>-0.1650369663725186</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2305668500358706</v>
+        <v>-0.106870229007626</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.349282296650713</v>
+        <v>7.497971844428541</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.575017946877274</v>
+        <v>7.747016706443937</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>16</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.157897876401861</v>
+        <v>2.156711089957206</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-10.73687350835326</v>
+        <v>-10.73702689835758</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.143351635235142</v>
+        <v>8.142857142857139</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.60506208213949</v>
+        <v>7.653608001905262</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>14.15243611177453</v>
+        <v>14.17639352072415</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>20.31772575250832</v>
+        <v>20.36573743149864</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>26.10065710872158</v>
+        <v>26.1499046711153</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>13.53967495219881</v>
+        <v>13.6129320619785</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>18.93975615586899</v>
+        <v>19.03910348116356</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>18.73505499760884</v>
+        <v>18.83496303362752</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.51943314996412</v>
+        <v>12.64312977099237</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>24.59928229665071</v>
+        <v>24.74797184442854</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.5750179468772</v>
+        <v>18.74701670644387</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4075</v>
+        <v>4086</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2793504728044098</v>
+        <v>-0.2778600561629005</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.09161276710197797</v>
+        <v>-0.0913367382517265</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1550086038010932</v>
+        <v>-0.1545885288188558</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2073215593793023</v>
+        <v>-0.2067522321428612</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1691788581152025</v>
+        <v>-0.1699573216601067</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.05433586961169823</v>
+        <v>-0.05479846755137885</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.02769315978952847</v>
+        <v>-0.02883867404737117</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.03321040448246748</v>
+        <v>0.03186948049950189</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1083024031792448</v>
+        <v>0.1061488793826086</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1054830497155237</v>
+        <v>0.1026731633151599</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1352511722041854</v>
+        <v>0.1323462569094431</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.06082387844094228</v>
+        <v>0.05751333263620495</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1206267519990973</v>
+        <v>0.1165184556348109</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1148952474907432</v>
+        <v>0.1102080916617254</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4041</v>
+        <v>4052</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3102204212595652</v>
+        <v>-0.3083898076668063</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.0580532708964796</v>
+        <v>-0.05785583917668902</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1680186218774082</v>
+        <v>-0.1675585252342415</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1971815664434615</v>
+        <v>-0.1966307941197272</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.154197177119805</v>
+        <v>-0.1554291810546502</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.08260405447644104</v>
+        <v>0.08156593451725769</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.110215871085444</v>
+        <v>0.1082848569729364</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1755891571525652</v>
+        <v>0.1734384315884796</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.2765755948088326</v>
+        <v>0.27333383668892</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2561962053127544</v>
+        <v>0.2521212326428497</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2385169165009842</v>
+        <v>0.2344698153784037</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1632001546635991</v>
+        <v>0.1585466432173277</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2023253446467592</v>
+        <v>0.1967135172634826</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1204274989683114</v>
+        <v>0.1142427676482569</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4003</v>
+        <v>4014</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2896809707733965</v>
+        <v>-0.2876136873155914</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.04477958312494934</v>
+        <v>-0.04460535316255232</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2516966274364307</v>
+        <v>-0.2510020536370448</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2823897054077733</v>
+        <v>-0.2815961374609515</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1591452957269581</v>
+        <v>-0.1608339568320432</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.07708083877527372</v>
+        <v>0.07582166592554529</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1057556776953987</v>
+        <v>0.1033648873554398</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2011185704327829</v>
+        <v>0.1984121338019094</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3036470080870757</v>
+        <v>0.299607851976063</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2412285791282827</v>
+        <v>0.236216472701642</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2253196007041538</v>
+        <v>0.2203252442323986</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1489587429728587</v>
+        <v>0.1431297709923669</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1424890898575129</v>
+        <v>0.1355808108046261</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.03267470430917285</v>
+        <v>0.0250436122734996</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3958</v>
+        <v>3969</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3278059826874653</v>
+        <v>-0.3252800820441877</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1878200077291652</v>
+        <v>-0.1872351547049789</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3926432236467434</v>
+        <v>-0.3915495114228662</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3495919131519614</v>
+        <v>-0.3485979966251449</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2188602773261508</v>
+        <v>-0.2209520785372163</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.03377165423655981</v>
+        <v>-0.03500954691477887</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.003837929711053789</v>
+        <v>-0.006495968903728055</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.09788213394867284</v>
+        <v>0.09487322457446368</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2022411898975633</v>
+        <v>0.1976074520137772</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1487415167978128</v>
+        <v>0.1428034559936648</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1349540130089579</v>
+        <v>0.1290214424895098</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.01844563791466669</v>
+        <v>-0.02527869035237984</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.02025546541041479</v>
+        <v>-0.02847651829186049</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1591912496866783</v>
+        <v>-0.1683272089000099</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3895</v>
+        <v>3906</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1523592239836873</v>
+        <v>-0.1498158310109901</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1376613762216721</v>
+        <v>-0.1371888589963888</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2882047935554723</v>
+        <v>-0.2873843147476336</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2977495171336173</v>
+        <v>-0.2968772800233452</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2330526719589088</v>
+        <v>-0.2359194565877516</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.04978013214039834</v>
+        <v>-0.05137857942914081</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.04362739972125951</v>
+        <v>-0.04698937657695978</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.0672682340741062</v>
+        <v>0.0635038531194283</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1486493111732088</v>
+        <v>0.1429116068519818</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1336520266050769</v>
+        <v>0.1260600029026904</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1999087687735042</v>
+        <v>0.1920876179201372</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.03349217721062558</v>
+        <v>-0.0423871174416135</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1055431653616097</v>
+        <v>-0.1160542625589187</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1733774318133854</v>
+        <v>-0.1597933293983829</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3804</v>
+        <v>3815</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2933341599553572</v>
+        <v>-0.2896311561304543</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1612845135352856</v>
+        <v>-0.1607046403799188</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2797961820098394</v>
+        <v>-0.2789767153988407</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3975503049850957</v>
+        <v>-0.396358543417378</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4758453398379956</v>
+        <v>-0.4792371863793008</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2953603205444608</v>
+        <v>-0.2968604682897222</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1821430483313051</v>
+        <v>-0.186329549139721</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.08372609337811099</v>
+        <v>-0.08831830716259503</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.02727012153463448</v>
+        <v>0.02000012480577595</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1634956516673114</v>
+        <v>0.1532694932086045</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2887718350135771</v>
+        <v>0.278126993816052</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1803632603161986</v>
+        <v>0.1676909446889923</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.06413117969933069</v>
+        <v>0.0493345278666979</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.01560680071531806</v>
+        <v>0.02486729622111028</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3722</v>
+        <v>3733</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3256282125959302</v>
+        <v>-0.3211102231785006</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1285241910861288</v>
+        <v>-0.1280018606436357</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3481111188541561</v>
+        <v>-0.347069633400281</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4177416123532822</v>
+        <v>-0.4164535704744097</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5395372209964435</v>
+        <v>-0.5438799724400525</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2007810464024118</v>
+        <v>-0.2031173052582105</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.217270224965489</v>
+        <v>-0.2224978626189653</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.07960040200798346</v>
+        <v>-0.08538551342598311</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.09897543685400478</v>
+        <v>-0.1076404366838375</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1125956620418336</v>
+        <v>0.1001149877196212</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1914308365349768</v>
+        <v>0.1786461171392517</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1604105935731468</v>
+        <v>0.144803131099458</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.1583072765056741</v>
+        <v>0.1396429745838645</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.07689865617332714</v>
+        <v>0.08240379457677705</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3600</v>
+        <v>3609</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.390082466424694</v>
+        <v>-0.3842145305744467</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.07548162498322597</v>
+        <v>-0.07506190092932741</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.5107028239531033</v>
+        <v>-0.5091263458713513</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.6149632206406821</v>
+        <v>-0.6130146449295424</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.8056670556481862</v>
+        <v>-0.8110133358504399</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2991723186192559</v>
+        <v>-0.3021107645951773</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2301244555360142</v>
+        <v>-0.2371386746960056</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.07165143733830348</v>
+        <v>-0.07934844091784754</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.03408302726271017</v>
+        <v>-0.04575637188974468</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2140482158356818</v>
+        <v>0.197420669096033</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4137553586196248</v>
+        <v>0.3964248276474009</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3805442610752365</v>
+        <v>0.3594825818480771</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.432615629984042</v>
+        <v>0.4231796006612285</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3250179468772458</v>
+        <v>0.3554955094364303</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3454</v>
+        <v>3463</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4751440247623435</v>
+        <v>-0.4813348464697143</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2526102067390497</v>
+        <v>-0.264849071240306</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.5740811318011012</v>
+        <v>-0.5855008401945696</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5438234080924147</v>
+        <v>-0.5552995391705053</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6620572475340509</v>
+        <v>-0.68332659907432</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3201072408266157</v>
+        <v>-0.3241106567463277</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.07111495289782255</v>
+        <v>-0.08094844746384666</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.03077724639693713</v>
+        <v>-0.04100048887312369</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.1845259791007905</v>
+        <v>0.1685837344122234</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5659135632763963</v>
+        <v>0.5432857713279731</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.580206951299111</v>
+        <v>0.5574096579783188</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6310428778158936</v>
+        <v>0.6030864809490808</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.73202694054185</v>
+        <v>0.7150619137126029</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6682431929687311</v>
+        <v>0.6918622161175989</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3236</v>
+        <v>3244</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1703799861720654</v>
+        <v>-0.173088454653282</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1321637568801535</v>
+        <v>-0.1406589500305344</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2328661100794776</v>
+        <v>-0.2408730522036961</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.02424010081173122</v>
+        <v>-0.06351404827859142</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.484080422487331</v>
+        <v>-0.5052589931686668</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3550461467876431</v>
+        <v>-0.4172025383891551</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.07081217226144787</v>
+        <v>0.0007851678707169185</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1763749228617897</v>
+        <v>0.1201079356672352</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3795452425015071</v>
+        <v>0.3295166015535429</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7825117938053481</v>
+        <v>0.7375943958540461</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6880834277694916</v>
+        <v>0.656644585829504</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.6915592315463286</v>
+        <v>0.6707021677884271</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7967483040672718</v>
+        <v>0.786107437648873</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.8370698628228581</v>
+        <v>0.8678551774673338</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2999</v>
+        <v>3006</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.08729900925775524</v>
+        <v>-0.06906233966612518</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4805616609046481</v>
+        <v>0.4914286979305871</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.6362136506620857</v>
+        <v>0.6143356805723386</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7847825836544402</v>
+        <v>0.7292933130699097</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1649821886640765</v>
+        <v>0.1403101295647886</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4140911234295501</v>
+        <v>0.3466062866815918</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5624809972636058</v>
+        <v>0.5186629634135826</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.8799708995277626</v>
+        <v>0.8174578626047122</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9043034093797857</v>
+        <v>0.8469746151700406</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.306422822535659</v>
+        <v>1.253199225844412</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.32091695159346</v>
+        <v>1.28177154426578</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.188572863201863</v>
+        <v>1.173714877375339</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.335277628427974</v>
+        <v>1.329697817158838</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.3609465897582</v>
+        <v>1.398380645232997</v>
       </c>
     </row>
     <row r="17">
@@ -2786,101 +2786,101 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2684</v>
+        <v>2688</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3815375010641517</v>
+        <v>0.3873621721412519</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.170077125193195</v>
+        <v>1.164979391703724</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6098526821229697</v>
+        <v>0.5687351834268455</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6489340691763417</v>
+        <v>0.5870950610727519</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3172735490046747</v>
+        <v>0.2837195260687935</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.5401874148273933</v>
+        <v>0.4821556025085343</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.8277778746230382</v>
+        <v>0.7932467251789888</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.030850705147536</v>
+        <v>0.9965589462082818</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.9907922706346071</v>
+        <v>0.9595863370714852</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.540352281055277</v>
+        <v>1.511222440271375</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.261135474508954</v>
+        <v>1.269907271545691</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.407287099293477</v>
+        <v>1.439598172479364</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.47148795983999</v>
+        <v>1.51210349188112</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.734481434209584</v>
+        <v>1.819933373110572</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003892</t>
+          <t>X &gt; -0.0003914</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2300</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8002660642070651</v>
+        <v>0.8116424087213474</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.362048245806427</v>
+        <v>1.380212393171767</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.208778665559826</v>
+        <v>1.184420298513388</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8607429395829698</v>
+        <v>0.836251319302157</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5398446908351033</v>
+        <v>0.564299005816558</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7067839378614877</v>
+        <v>0.7067064281556981</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.361204013377929</v>
+        <v>1.384859552315717</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.85065710872162</v>
+        <v>1.875132832784189</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.833153213068414</v>
+        <v>1.881619589140648</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.374538764564647</v>
+        <v>2.448490704110107</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.169837606304455</v>
+        <v>2.244350256574016</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.334650541268466</v>
+        <v>2.432895090418704</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.131890992302885</v>
+        <v>2.255033991321199</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.357626642529418</v>
+        <v>2.52962540209608</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>1949</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.008565754996695</v>
+        <v>1.979369960644064</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.398405829198126</v>
+        <v>2.39721904275347</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.465409713811994</v>
+        <v>2.465256323807672</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.390401404347507</v>
+        <v>2.389906911969504</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.749495124725385</v>
+        <v>1.798041044491157</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.533785521728355</v>
+        <v>1.557742930677968</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.475242427726421</v>
+        <v>2.523254106716742</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.726490869624655</v>
+        <v>2.775738432018372</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.870742166154727</v>
+        <v>2.943999275934424</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.303532451405168</v>
+        <v>3.402879776699741</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.842289476828917</v>
+        <v>2.942197512847592</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.081901082237081</v>
+        <v>3.205597703265326</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.559133502397245</v>
+        <v>2.707823050175072</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.630944062834146</v>
+        <v>2.802942822400809</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>1623</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.479034678030033</v>
+        <v>2.449838883677401</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.531434536907057</v>
+        <v>2.530247750462401</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.643748796021391</v>
+        <v>1.64359540601707</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.465902467028116</v>
+        <v>1.465407974650113</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9276129139324212</v>
+        <v>0.976158833698193</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7936868819532137</v>
+        <v>0.8176442909028268</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.818033823980947</v>
+        <v>1.866045502971268</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.336793892455447</v>
+        <v>2.386041454849163</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.522268913997991</v>
+        <v>2.595526023777687</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.151093186059995</v>
+        <v>3.250440511354569</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.008006322316135</v>
+        <v>3.10791435833481</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.227227358220439</v>
+        <v>3.350923979248684</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.299990861037649</v>
+        <v>3.448680408815477</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.971197860617231</v>
+        <v>3.143196620183893</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>1326</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.571874316373645</v>
+        <v>2.542678522021014</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.751035131303787</v>
+        <v>3.749848344859132</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.205434183954466</v>
+        <v>3.205280793950145</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.18482976494856</v>
+        <v>3.184335272570557</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.34488108666433</v>
+        <v>2.393427006430102</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.038936865922345</v>
+        <v>2.062894274871958</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.613351695193138</v>
+        <v>3.661363374183459</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.523356957892069</v>
+        <v>3.572604520285786</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.914863489152097</v>
+        <v>3.988120598931793</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.196166412279247</v>
+        <v>4.29551373757382</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.916050472721921</v>
+        <v>4.015958508740596</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.176672968968646</v>
+        <v>4.30036958999689</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.058181240843773</v>
+        <v>4.2068707886216</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.057672547178903</v>
+        <v>4.229671306745566</v>
       </c>
     </row>
     <row r="22">
@@ -3046,205 +3046,205 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.735300185681865</v>
+        <v>3.74551373766927</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.826816795320738</v>
+        <v>4.77259767861603</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.612225590745872</v>
+        <v>4.558877692101504</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.832540824424328</v>
+        <v>4.86877973511637</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.57353055060792</v>
+        <v>3.659458586963723</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.780814490152913</v>
+        <v>3.75222610398248</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5.227635662418272</v>
+        <v>5.221723030058541</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>5.0308372889018</v>
+        <v>5.025917272375473</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.879765042288938</v>
+        <v>4.89893566233858</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>5.471287687400526</v>
+        <v>5.515251095925045</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>5.5368567994106</v>
+        <v>5.581137651089222</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>6.02168540221637</v>
+        <v>6.089349392954567</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5.601534548902961</v>
+        <v>5.694191466390741</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5.466909838769141</v>
+        <v>5.583200324805745</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.06906</t>
+          <t>X &gt; 0.06905</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>930</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.433062464089296</v>
+        <v>3.403866669736665</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.187467768874932</v>
+        <v>4.186280982430276</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.975492083044628</v>
+        <v>4.975338693040307</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.213244108353422</v>
+        <v>5.212749615975419</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.567427673537296</v>
+        <v>4.615973593303067</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.972328584892814</v>
+        <v>4.996285993842427</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6.285467687992231</v>
+        <v>6.333479366982552</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.818399044205492</v>
+        <v>5.867646606599209</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.864943769403148</v>
+        <v>5.938200879182844</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>6.412874435438887</v>
+        <v>6.51222176073346</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.993119513737831</v>
+        <v>6.093027549756506</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.78018583813617</v>
+        <v>6.903882459164414</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6.682615629984042</v>
+        <v>6.83130517776187</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6.263189989887991</v>
+        <v>6.435188749454653</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.08295</t>
+          <t>X &gt; 0.08294</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>772</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.607166871020048</v>
+        <v>3.577971076667417</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5.234322746868138</v>
+        <v>5.233135960423482</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.616753434651962</v>
+        <v>5.61660004464764</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.653714329535653</v>
+        <v>6.65321983715765</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.467756382657583</v>
+        <v>5.516302302423355</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.412798806075045</v>
+        <v>6.436756215024658</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.234824198104221</v>
+        <v>7.282835877094541</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>7.933558663125773</v>
+        <v>7.982806225519489</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>7.613509149090042</v>
+        <v>7.686766258869739</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.281725067786091</v>
+        <v>7.381072393080665</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>7.077023909525899</v>
+        <v>7.176931945544574</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>8.018137813176558</v>
+        <v>8.141834434204803</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.857054317376097</v>
+        <v>8.005743865153924</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.823722610089682</v>
+        <v>7.995721369656344</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.09685</t>
+          <t>X &gt; 0.09683</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>653</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.261809850016952</v>
+        <v>3.232614055664321</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.253992822803049</v>
+        <v>4.252806036358393</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.39061500619502</v>
+        <v>5.390461616190699</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.520840149783382</v>
+        <v>5.520345657405379</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.829411239872982</v>
+        <v>4.877957159638754</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5.892482053581581</v>
+        <v>5.916439462531194</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.186025905647725</v>
+        <v>7.234037584638045</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.484654045934491</v>
+        <v>7.533901608328208</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.883089959855823</v>
+        <v>7.95634706963552</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.186310520340669</v>
+        <v>7.285657845635242</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.287888075709866</v>
+        <v>7.387796111728541</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.394241725768104</v>
+        <v>8.517938346796349</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8.586648299713502</v>
+        <v>8.73533784749133</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>8.352965879495933</v>
+        <v>8.524964639062595</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>540</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.815380265761945</v>
+        <v>3.786184471409314</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.68567565417959</v>
+        <v>3.684488867734935</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.06868204720233</v>
+        <v>6.068528657198009</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.754462746346256</v>
+        <v>6.753968253968253</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.660617637694997</v>
+        <v>5.709163557460769</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.513547222885649</v>
+        <v>6.537504631835262</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.354762789545404</v>
+        <v>7.402774468535725</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>7.99880525686978</v>
+        <v>8.048052819263496</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>9.048934211458118</v>
+        <v>9.122191321237814</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.199015415128258</v>
+        <v>8.298362740422832</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.994314256868066</v>
+        <v>8.094222292886741</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.769433149964122</v>
+        <v>8.893129770992367</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9.460393407761828</v>
+        <v>9.609082955539655</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.315758687617993</v>
+        <v>9.487757447184656</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>449</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.643805573029127</v>
+        <v>3.614609778676495</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.368922375288236</v>
+        <v>3.36773558884358</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>7.651211124163481</v>
+        <v>7.65105773415916</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.226870566192822</v>
+        <v>8.226376073814819</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.906843819333211</v>
+        <v>5.955389739098983</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.204217848968298</v>
+        <v>6.228175257917911</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.455810385025067</v>
+        <v>7.503822064015388</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.770478935002245</v>
+        <v>8.819726497395962</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>9.600365375361434</v>
+        <v>9.673622485141131</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.750446579031575</v>
+        <v>8.849793904326148</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.768462569991868</v>
+        <v>8.868370606010544</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>10.36186076689064</v>
+        <v>10.48555738791888</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.05529565967966</v>
+        <v>11.20398520745749</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>9.94472841458326</v>
+        <v>10.11672717414992</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>374</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.936196268930892</v>
+        <v>3.907000474578261</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.464047609022138</v>
+        <v>4.462860822577483</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.079971411432872</v>
+        <v>8.079818021428551</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.08185430903193</v>
+        <v>10.08135981665393</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7.404527322781163</v>
+        <v>7.453073242546935</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.434521673271867</v>
+        <v>7.45847908222148</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8.151950351438842</v>
+        <v>8.199962030429162</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.556539461662801</v>
+        <v>9.605787024056518</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>10.29769634257318</v>
+        <v>10.37095345235287</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.982536904532097</v>
+        <v>10.08188422982667</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.84735446284944</v>
+        <v>10.94726249886811</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.68387165263793</v>
+        <v>11.80756827366617</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>12.86799887419082</v>
+        <v>13.01668842196865</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.95469709126227</v>
+        <v>11.12669585082893</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>304</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.453294495781435</v>
+        <v>2.424098701428804</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.815792613243921</v>
+        <v>2.814605826799266</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>6.368389649541513</v>
+        <v>6.368236259537191</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.47229900365619</v>
+        <v>8.471804511278187</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.302430503192078</v>
+        <v>5.350976422957849</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.257699269669267</v>
+        <v>6.28165667861888</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.159831015666263</v>
+        <v>7.207842694656584</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.00855184556373</v>
+        <v>8.057799407957447</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.263359162725166</v>
+        <v>9.336616272504862</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.071335103237416</v>
+        <v>9.17068242853199</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.853476050240374</v>
+        <v>9.953384086259049</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.2036436762799</v>
+        <v>11.32734029730815</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.09928229665071</v>
+        <v>12.24797184442854</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.35133373635093</v>
+        <v>10.52333249591759</v>
       </c>
     </row>
     <row r="30">
@@ -3462,49 +3462,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1939810888072131</v>
+        <v>0.3587406341294042</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.640408164467658</v>
+        <v>0.8247438768424118</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.537817849671477</v>
+        <v>3.709694413117866</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.371746696963534</v>
+        <v>7.528103044496483</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.3643213413987</v>
+        <v>4.579837510101946</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.484740638523512</v>
+        <v>5.672295160068401</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.811552913002195</v>
+        <v>6.021475136416718</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.990574804194871</v>
+        <v>7.194986638328459</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.752637915161813</v>
+        <v>7.977686160339204</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.960332287556241</v>
+        <v>8.793201841819311</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.755631129296049</v>
+        <v>8.998897459856977</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.69640845951695</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.25051686455195</v>
+        <v>11.12092266410067</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.65320724728877</v>
+        <v>10.96013146054226</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>198</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.054437504819184</v>
+        <v>1.025241710466553</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.5567485882446448</v>
+        <v>-0.5579353746893005</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.05858103710131957</v>
+        <v>0.05842764709699821</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.744361736245239</v>
+        <v>5.743867243867236</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.670718647796008</v>
+        <v>1.71926456756178</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.473143182481607</v>
+        <v>2.49710059143122</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.398533833316442</v>
+        <v>3.446545512306763</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.941566199630721</v>
+        <v>3.990813762024437</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.890685053208948</v>
+        <v>4.963942162988644</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.071069287182119</v>
+        <v>7.170416612476693</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.361317623871429</v>
+        <v>6.461225659890104</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.415897796428773</v>
+        <v>8.539594417457018</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.51089845826688</v>
+        <v>9.659588006044707</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.736634108493412</v>
+        <v>9.908632868060074</v>
       </c>
     </row>
     <row r="32">
@@ -3569,202 +3569,202 @@
         <v>155</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2228515144053205</v>
+        <v>-0.2520473087579518</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.834037607469149</v>
+        <v>-1.835224393913805</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.3518361690661322</v>
+        <v>0.3516827790618109</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.578835506202886</v>
+        <v>7.578341013824883</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.169578211171711</v>
+        <v>3.218124130937483</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.466952240806798</v>
+        <v>3.490909649756411</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.382241881540629</v>
+        <v>3.43025356053095</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.915173237753891</v>
+        <v>2.964420800147607</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.499352371553684</v>
+        <v>3.57260948133338</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.520401317159319</v>
+        <v>6.619748642453892</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.960861449221696</v>
+        <v>7.060769485240371</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.995239601577019</v>
+        <v>7.118936222605264</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>8.510572619231354</v>
+        <v>8.659262167009182</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.445985688812726</v>
+        <v>7.617984448379389</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.208</t>
+          <t>X &gt; 0.2079</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.3190839694656518</v>
+        <v>0.2898881751130205</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.292102123598177</v>
+        <v>-1.293288910042833</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.313126491646777</v>
+        <v>2.312973101642456</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.04335163523514</v>
+        <v>8.042857142857137</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.705062082139442</v>
+        <v>2.753608001905214</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.202436111774531</v>
+        <v>2.226393520724145</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.91772575250836</v>
+        <v>2.965737431498681</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.250657108721626</v>
+        <v>3.299904671115343</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.18967495219885</v>
+        <v>3.262932061978546</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.539756155868993</v>
+        <v>5.639103481163566</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.3350549976088</v>
+        <v>5.434963033627476</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>3.893129770992367</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.149282296650711</v>
+        <v>4.297971844428538</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.975017946877244</v>
+        <v>2.147016706443907</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.2219</t>
+          <t>X &gt; 0.2218</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.519083969465647</v>
+        <v>1.489888175113016</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.907897876401826</v>
+        <v>1.90671108995717</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.513126491646773</v>
+        <v>2.512973101642451</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.643351635235142</v>
+        <v>7.642857142857139</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.105062082139455</v>
+        <v>1.153608001905226</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.5975638882254657</v>
+        <v>-0.5736064792758526</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.317725752508359</v>
+        <v>3.36573743149868</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.85065710872162</v>
+        <v>2.899904671115337</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.789674952198844</v>
+        <v>2.86293206197854</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.939756155868992</v>
+        <v>5.039103481163565</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.735054997608799</v>
+        <v>6.834963033627474</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.769433149964122</v>
+        <v>4.893129770992367</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.5750179468772387</v>
+        <v>0.7470167064439011</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.2358</t>
+          <t>X &gt; 0.2357</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.280988731370414</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.860278828782775</v>
+        <v>1.859092042338119</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5.036936015456305</v>
+        <v>5.036782625451984</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.548113539997047</v>
+        <v>7.547619047619044</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1330331559557862</v>
+        <v>-0.08448723619001441</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-3.407087697749276</v>
+        <v>-3.383130288799663</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.0796305144131324</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-1.577914319849803</v>
+        <v>-1.528666757456087</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.7420559045798072</v>
+        <v>0.8153130143595035</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>2.273089489202327</v>
+        <v>2.372436814496901</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.449340711894507</v>
+        <v>4.549248747913182</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3.293242673773648</v>
+        <v>3.416939294801892</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.6983367509683305</v>
+        <v>-0.5496472031905029</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-2.853553481694185</v>
+        <v>-2.681554722127522</v>
       </c>
     </row>
   </sheetData>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>14.1857506361323</v>
+        <v>14.15655484177967</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.812659781163724</v>
+        <v>7.811472994719068</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.417888396408685</v>
+        <v>7.417735006404364</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.11954211142562</v>
+        <v>11.11904761904762</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.390776367853739</v>
+        <v>9.439322287619511</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.92624563558406</v>
+        <v>4.950203044533673</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.841535276317892</v>
+        <v>4.889546955308212</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.8030380611025834</v>
+        <v>0.8522856234963001</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.63889647637258</v>
+        <v>-1.565639366592883</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.298339082226242</v>
+        <v>-1.198991756931669</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-2.693516430962632</v>
+        <v>-2.593608394943956</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.88881294144452</v>
+        <v>-1.740123393666693</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.853553481694185</v>
+        <v>-2.681554722127522</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>118</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11.07840600336395</v>
+        <v>11.04921020901132</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.382474147588262</v>
+        <v>4.381287361143606</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.682618017070503</v>
+        <v>5.682464627066182</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.507758414896159</v>
+        <v>7.507263922518156</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.122011234681821</v>
+        <v>6.170557154447593</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.207733379750884</v>
+        <v>-1.183775970801271</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.292443739017052</v>
+        <v>-1.244432060026732</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.301885264159729</v>
+        <v>-4.252637701766012</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-6.905240302038436</v>
+        <v>-6.83198319225874</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-5.417487375272557</v>
+        <v>-5.317579339253882</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.840736341561296</v>
+        <v>-2.717039720533052</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.108344821993349</v>
+        <v>-3.959655274215521</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.187693917529536</v>
+        <v>-2.015695157962874</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>156</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.775494225875903</v>
+        <v>7.746298431523272</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.95917992768387</v>
+        <v>2.957993141239214</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.410562389082671</v>
+        <v>6.410408999078349</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.822838814722324</v>
+        <v>7.822344322344321</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.720446697524061</v>
+        <v>4.768992617289832</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.751410042071619</v>
+        <v>-0.7274526331220059</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.8361204013377872</v>
+        <v>-0.7881087223474665</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.867291609227095</v>
+        <v>-3.818044046833379</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.851350688826784</v>
+        <v>-5.778093579047088</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.137166921054082</v>
+        <v>-4.037819595759508</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.700842438288632</v>
+        <v>-3.600934402269957</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.743387362856396</v>
+        <v>-1.619690741828151</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.522512575144155</v>
+        <v>-1.373823027366328</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.6262999981592969</v>
+        <v>0.7982987577259593</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>201</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.723064068968135</v>
+        <v>6.693868274615504</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.111877975904306</v>
+        <v>5.110691189459651</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.702181218014935</v>
+        <v>7.702027828010614</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.33489392379235</v>
+        <v>7.334399431414347</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.806554619452875</v>
+        <v>4.855100539218647</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.621341584411347</v>
+        <v>1.64529899336096</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.536631225145179</v>
+        <v>1.584642904135499</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.920487169885341</v>
+        <v>-0.8712396074916242</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.474006639840944</v>
+        <v>-2.400749530061248</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.333875684927037</v>
+        <v>-1.234528359632463</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.041064405376275</v>
+        <v>-0.9411563693575999</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.978388373844723</v>
+        <v>2.102084994872968</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.055749958342254</v>
+        <v>2.204439506120082</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.271535359812567</v>
+        <v>4.44353411937923</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>264</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.44332639370807</v>
+        <v>2.414130599355438</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.104867573371521</v>
+        <v>3.103680786926866</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.225247703767998</v>
+        <v>4.225094313763677</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.734260726144235</v>
+        <v>4.733766233766232</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.817183294260666</v>
+        <v>3.865729214026437</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.46304217238059</v>
+        <v>1.486999581330203</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.757119691902311</v>
+        <v>1.805131370892632</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2251004670359507</v>
+        <v>-0.1758529046422339</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.043658381134485</v>
+        <v>-0.9704012713547883</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.757213541100711</v>
+        <v>-0.6578662158061377</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.719490456936661</v>
+        <v>-1.619582420917986</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.723978604509583</v>
+        <v>1.847675225537827</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.818979266347682</v>
+        <v>2.96766881412551</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.423502795362097</v>
+        <v>3.216713676140877</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>355</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.293731856789591</v>
+        <v>3.26453606243696</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.527616186260978</v>
+        <v>2.526429399816323</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.977915224041148</v>
+        <v>2.977761834036826</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.516591071854862</v>
+        <v>4.516096579476859</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.386752222984512</v>
+        <v>5.435298142750284</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.71229526670411</v>
+        <v>3.736252675653724</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.782514484902734</v>
+        <v>2.830526163893055</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.470375418580787</v>
+        <v>1.519622980974503</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5643228395227951</v>
+        <v>0.6375799493024914</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.8489762384972011</v>
+        <v>-0.7496289132026277</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.180437960137688</v>
+        <v>-2.080529924119013</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.01929924440207</v>
+        <v>-0.8956026233738257</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.2506907473549376</v>
+        <v>0.3993802951327652</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.47642639758147</v>
+        <v>0.3667350163030676</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>437</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.89665834017503</v>
+        <v>2.867462545822399</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.743138151001361</v>
+        <v>1.741951364556705</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.950197429861888</v>
+        <v>2.950044039857566</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.766921429285489</v>
+        <v>3.766426936907486</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.830462539805346</v>
+        <v>4.879008459571118</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.153008194154395</v>
+        <v>2.176965603104009</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.525963738778394</v>
+        <v>2.573975417768715</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.143563287211329</v>
+        <v>1.192810849605046</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.540247034578712</v>
+        <v>1.613504144358409</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2250035695314665</v>
+        <v>-0.1256562442368931</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.8873706316818186</v>
+        <v>-0.7874625956631434</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.6241595273814156</v>
+        <v>-0.5004629063531709</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.5866444768046648</v>
+        <v>-0.4379549290268372</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1320758746330526</v>
+        <v>-0.1889100670114701</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.599297873208961</v>
+        <v>2.57010207885633</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.9881117801451325</v>
+        <v>0.9869249937004767</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.267137186833942</v>
+        <v>3.266983796829621</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.110374808140669</v>
+        <v>4.109880315762666</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.354616449340874</v>
+        <v>5.403162369106646</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.265181209813747</v>
+        <v>2.28913861876336</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.002217731117995</v>
+        <v>2.050229410108315</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.8221366096128904</v>
+        <v>0.8713841720066071</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7611544530901142</v>
+        <v>0.8344115628698106</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.8017768209581035</v>
+        <v>-0.7024294956635302</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.075996695795837</v>
+        <v>-1.976088659777162</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.863365424010922</v>
+        <v>-1.739668802982678</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.186431989063578</v>
+        <v>-2.134826729546504</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.684373824142426</v>
+        <v>-1.885781867531136</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.398857661120523</v>
+        <v>2.433390999971778</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.636327862257552</v>
+        <v>1.697671541934561</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.797426350204063</v>
+        <v>2.857605870004036</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.846246973365616</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.379460950597725</v>
+        <v>3.486941335238555</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.838079676130967</v>
+        <v>1.86203708508058</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.7632703069638183</v>
+        <v>0.8112819859541389</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4376443788772164</v>
+        <v>0.4868919412709332</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.4719940718464102</v>
+        <v>-0.3987369620667138</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.312011878077257</v>
+        <v>-2.212664552782684</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.375270320637313</v>
+        <v>-2.275362284618637</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.623777599682278</v>
+        <v>-2.500080978654033</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.10964121609716</v>
+        <v>-3.036681620917989</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.949804748158215</v>
+        <v>-3.070522190302903</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6508334295088432</v>
+        <v>0.6585240505158083</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.7675091075033293</v>
+        <v>0.7939291350699449</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.8047031655128762</v>
+        <v>0.8298366891827342</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1789887842632254</v>
+        <v>0.3152524167561737</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.800526444990417</v>
+        <v>1.866819602334864</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.449952310478643</v>
+        <v>1.662952660509092</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.06934562291872481</v>
+        <v>0.3119739906384709</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.397723020868014</v>
+        <v>-0.2023558240407297</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.9986619808465065</v>
+        <v>-0.8267231104352462</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.388537580632089</v>
+        <v>-2.239213670940003</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.053281935436559</v>
+        <v>-1.953373899417883</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.068404687873716</v>
+        <v>-2.003198522744135</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.429938482570059</v>
+        <v>-2.398356449307961</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.6871705688324</v>
+        <v>-2.797259751439462</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2682248629364423</v>
+        <v>0.2202636017341746</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.9993186184435388</v>
+        <v>-1.021616555094027</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.651821961961467</v>
+        <v>-1.586003007572558</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.951150082977911</v>
+        <v>-1.797415894685521</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3416733130495615</v>
+        <v>-0.2776473354133131</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9034058126240936</v>
+        <v>-0.7274526331220059</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.199901074662748</v>
+        <v>-1.084219796901657</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.096892332378971</v>
+        <v>-1.932287109706571</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.071889966115847</v>
+        <v>-1.923700328766948</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.093777808017506</v>
+        <v>-2.959181252970225</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.1265099207059</v>
+        <v>-3.031989756072093</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.788226058297489</v>
+        <v>-2.756354765090109</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.162345610326035</v>
+        <v>-3.151512691653934</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.32153377726069</v>
+        <v>-3.417931747164339</v>
       </c>
     </row>
     <row r="17">
@@ -4480,101 +4480,101 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1475</v>
+        <v>1482</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.6590536823562161</v>
+        <v>-0.6657120931633074</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.93285785909076</v>
+        <v>-1.913543772551222</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.113054345060377</v>
+        <v>-1.032969218947748</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.117781968003726</v>
+        <v>-1.001438159156287</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.5089730055798469</v>
+        <v>-0.4474665447704069</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.8500959611491652</v>
+        <v>-0.7429613179855252</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.303895869113255</v>
+        <v>-1.238163039247787</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.734873655308121</v>
+        <v>-1.668063027404173</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.593016055238607</v>
+        <v>-1.534374335327847</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.578161355963324</v>
+        <v>-2.524238836895734</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.070087086288353</v>
+        <v>-2.085468524025934</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.337540445161132</v>
+        <v>-2.395669149385505</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.45017569792924</v>
+        <v>-2.520921542885901</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.001253239563432</v>
+        <v>-3.149069663326678</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003892</t>
+          <t>X &lt; -0.0003914</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1859</v>
+        <v>1870</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.9576664313895122</v>
+        <v>-0.9675586333976227</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.525257203812089</v>
+        <v>-1.540097420681128</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.49222110193611</v>
+        <v>-1.455112004740528</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.012614121854213</v>
+        <v>-0.9776856990800553</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6122826716078791</v>
+        <v>-0.6397892291916918</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7678906155955829</v>
+        <v>-0.7643363673951953</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.52043073195037</v>
+        <v>-1.542578133533304</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.173471577605454</v>
+        <v>-2.19342866221799</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.098737064968532</v>
+        <v>-2.148807532471828</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.75911662996031</v>
+        <v>-2.837564965179197</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.505546506150594</v>
+        <v>-2.585977137312696</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.710953738805351</v>
+        <v>-2.819857936116129</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.457169316252504</v>
+        <v>-2.598284840063435</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.793997652907592</v>
+        <v>-2.990951207994598</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2210</v>
+        <v>2221</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.738675814609927</v>
+        <v>-1.704382191941598</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.976890602446062</v>
+        <v>-1.966105748376911</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.168098181923689</v>
+        <v>-2.157277794414881</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.05935106746756</v>
+        <v>-2.048760965614392</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.492504389244061</v>
+        <v>-1.528006347870559</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.261224844041521</v>
+        <v>-1.276163679814204</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.043573300265656</v>
+        <v>-2.075914274066847</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.306382602469711</v>
+        <v>-2.338532688561358</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.388654618907239</v>
+        <v>-2.441650148264038</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.763044205467956</v>
+        <v>-2.83730101321845</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.356223809440451</v>
+        <v>-2.433022577883314</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.568722365406579</v>
+        <v>-2.665574682448927</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.105263157894747</v>
+        <v>-2.226600612817187</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.216837256742664</v>
+        <v>-2.358341240426874</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2536</v>
+        <v>2547</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.558985861840746</v>
+        <v>-1.533549324886984</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.501835247617016</v>
+        <v>-1.494617554044396</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.051459295553848</v>
+        <v>-1.046839251758641</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.9002461652361831</v>
+        <v>-0.896055645566797</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.5530911595108421</v>
+        <v>-0.5819162547457992</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4308972215588014</v>
+        <v>-0.4444479665556997</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.044838148396074</v>
+        <v>-1.071224197318855</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.412128099775622</v>
+        <v>-1.437737318700556</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.491316783338341</v>
+        <v>-1.53205226404026</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.887015497674319</v>
+        <v>-1.94286437457928</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.794681118972534</v>
+        <v>-1.851311476176448</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.935846597868817</v>
+        <v>-2.007223308646708</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.979846595741876</v>
+        <v>-2.067177292149168</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.811417384353035</v>
+        <v>-1.914545916249459</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2833</v>
+        <v>2844</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.180845756465487</v>
+        <v>-1.162544446518062</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.649219874037549</v>
+        <v>-1.642308517885972</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.498125266440425</v>
+        <v>-1.492280838812881</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.454784136836615</v>
+        <v>-1.44894383822205</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.059610683518542</v>
+        <v>-1.078428450951421</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8840827196228602</v>
+        <v>-0.8919795508046064</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.583682698195865</v>
+        <v>-1.600239418729302</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.574140355174116</v>
+        <v>-1.591323399060094</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.721952954777898</v>
+        <v>-1.74991455086807</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.848047862460234</v>
+        <v>-1.887862810971264</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.716284917764966</v>
+        <v>-1.756888037675651</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.839032458501485</v>
+        <v>-1.890426096892384</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.781275219227908</v>
+        <v>-1.844734658207656</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.818557767912736</v>
+        <v>-1.892927034765655</v>
       </c>
     </row>
     <row r="22">
@@ -4740,205 +4740,205 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3049</v>
+        <v>3059</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.337872268287455</v>
+        <v>-1.338236824886984</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.65825697495395</v>
+        <v>-1.63480633107833</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.676415992013347</v>
+        <v>-1.653150676859177</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.72506941739644</v>
+        <v>-1.734138621235395</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.265114503864474</v>
+        <v>-1.293588869020468</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.310027087440382</v>
+        <v>-1.296788742073375</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.80269309565918</v>
+        <v>-1.796689182982725</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.761454184240726</v>
+        <v>-1.755886519749261</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.67397927176971</v>
+        <v>-1.677537911911791</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.884023732765137</v>
+        <v>-1.896254011490697</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.907146837253585</v>
+        <v>-1.919445849455478</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.084385270225987</v>
+        <v>-2.104910085263754</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.929406227939445</v>
+        <v>-1.959544495440745</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.915306749744595</v>
+        <v>-1.954192839159234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.06906</t>
+          <t>X &lt; 0.06905</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3229</v>
+        <v>3240</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.9695033223295439</v>
+        <v>-0.9576986678012176</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.114626035970907</v>
+        <v>-1.110509082244562</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.431317952797663</v>
+        <v>-1.426430158892757</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.46995494086859</v>
+        <v>-1.464835164835165</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.281596348990874</v>
+        <v>-1.291452016562005</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.369266081614406</v>
+        <v>-1.371636035926095</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.715648783956404</v>
+        <v>-1.72388375729097</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.609930217398933</v>
+        <v>-1.618887688712135</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.592514287133241</v>
+        <v>-1.60856254510928</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.745366021675089</v>
+        <v>-1.7685414016971</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.623855893480311</v>
+        <v>-1.647614826378692</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.851117763065901</v>
+        <v>-1.881083677496221</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.820996341120185</v>
+        <v>-1.858399645852238</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.733126989635608</v>
+        <v>-1.777674651580789</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.08295</t>
+          <t>X &lt; 0.08294</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3387</v>
+        <v>3398</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.8044454422990626</v>
+        <v>-0.7950722470505767</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.105929719950048</v>
+        <v>-1.10208656400178</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.279104232308484</v>
+        <v>-1.274941242740063</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.486468794555847</v>
+        <v>-1.481556002682765</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.214136975575506</v>
+        <v>-1.221502065602856</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.401687599565669</v>
+        <v>-1.402731552675732</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.559115732465116</v>
+        <v>-1.565246415784713</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.745275694107725</v>
+        <v>-1.751094153796529</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.643108066669079</v>
+        <v>-1.654846368817807</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.563045377601959</v>
+        <v>-1.581119916837615</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.515682465518047</v>
+        <v>-1.534046081338708</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.730714386182228</v>
+        <v>-1.753929052537039</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.692040017398881</v>
+        <v>-1.721210267957453</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.715799886013215</v>
+        <v>-1.750334676722666</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.09685</t>
+          <t>X &lt; 0.09683</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3506</v>
+        <v>3517</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.5911746267264562</v>
+        <v>-0.5837662158218251</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7094983714662817</v>
+        <v>-0.7070605167302872</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.003791336047279</v>
+        <v>-1.000632340534416</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.000561902876349</v>
+        <v>-0.9973469966381856</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8693333659402143</v>
+        <v>-0.8758871767674989</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.040364115886248</v>
+        <v>-1.041691585658839</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.252157538126419</v>
+        <v>-1.257418073609138</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.333853141847847</v>
+        <v>-1.339096180431632</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.379507616869795</v>
+        <v>-1.38919740991242</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.245429029316192</v>
+        <v>-1.260527305544755</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.263520095010179</v>
+        <v>-1.278673330008893</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.47001952962539</v>
+        <v>-1.489081084364265</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.503868544524082</v>
+        <v>-1.52761087302455</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.490583878564856</v>
+        <v>-1.51883487160557</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3619</v>
+        <v>3630</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.55360325520396</v>
+        <v>-0.5474436942254428</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.4705102756224093</v>
+        <v>-0.4689067024645794</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9056062907223605</v>
+        <v>-0.9028467280746497</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.981062804004317</v>
+        <v>-0.9780219780219852</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8155553379267104</v>
+        <v>-0.8205607257672156</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.916836013949208</v>
+        <v>-0.9177516139652369</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.014320579537966</v>
+        <v>-1.018645301523037</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.135549787830101</v>
+        <v>-1.139699289280692</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.26440893301087</v>
+        <v>-1.271868488227774</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.133387647608785</v>
+        <v>-1.145266359232693</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.102051573346479</v>
+        <v>-1.114114863427304</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.218139343822124</v>
+        <v>-1.233522211386486</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.319225990642103</v>
+        <v>-1.338161452183961</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.326888657157014</v>
+        <v>-1.349402026338467</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3710</v>
+        <v>3721</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4261215099864089</v>
+        <v>-0.4211991307252205</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3306835314434267</v>
+        <v>-0.3295600056763774</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.9260027746794677</v>
+        <v>-0.9232541223661173</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9695515905713137</v>
+        <v>-0.966630930045568</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6868174553706368</v>
+        <v>-0.6908960195424996</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6976176805869514</v>
+        <v>-0.6985729582246307</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.821633946173371</v>
+        <v>-0.8252496929648387</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.005101771795054</v>
+        <v>-1.008332516971585</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.078427335822688</v>
+        <v>-1.084464610055811</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.9713908554395658</v>
+        <v>-0.9810307470243629</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9727284658978022</v>
+        <v>-0.982437610840833</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.165911677622084</v>
+        <v>-1.178049385601774</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.247861330403992</v>
+        <v>-1.262909402213054</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.141963185198229</v>
+        <v>-1.160266282000059</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3785</v>
+        <v>3796</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3745442559161347</v>
+        <v>-0.3704426203713567</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.3654758396898288</v>
+        <v>-0.3642973134041867</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.798780779164602</v>
+        <v>-0.796456895730806</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.970614109165389</v>
+        <v>-0.9677576758501658</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.7041102952986122</v>
+        <v>-0.7071015907360376</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6824571125861354</v>
+        <v>-0.6829650492022452</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.726578044959993</v>
+        <v>-0.7294505779675262</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.8892532051797204</v>
+        <v>-0.8917839138399373</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.9359187153473201</v>
+        <v>-0.9408037970059269</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.9005711072611149</v>
+        <v>-0.9082649398890723</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.9851139569846552</v>
+        <v>-0.9926231732690809</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.06816917377499</v>
+        <v>-1.077907617106632</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.183205817453882</v>
+        <v>-1.195206980959931</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.022075844404128</v>
+        <v>-1.036966433703611</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3855</v>
+        <v>3866</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1799853169872989</v>
+        <v>-0.1770362899553035</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1484765740765894</v>
+        <v>-0.1479562643491832</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.5034280867287961</v>
+        <v>-0.5019869189920527</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6438411202629197</v>
+        <v>-0.64197257850509</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.391832327798447</v>
+        <v>-0.3947790948689729</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4427619208426066</v>
+        <v>-0.4435083894462153</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4875564846744425</v>
+        <v>-0.4901882075408182</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5779883199238043</v>
+        <v>-0.5804672297110969</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6507395555731676</v>
+        <v>-0.6550219550713052</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.631376261855813</v>
+        <v>-0.6378991028157657</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.692109336242936</v>
+        <v>-0.6985081475562964</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.7988841951227243</v>
+        <v>-0.8069736416239763</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8675226826023987</v>
+        <v>-0.8775130275652572</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7570183695948671</v>
+        <v>-0.7692792066445548</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3916</v>
+        <v>3926</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.0006314370146398574</v>
+        <v>-0.009477146034484463</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.03213412894763934</v>
+        <v>0.02047442159759072</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2215310077166066</v>
+        <v>-0.2325183893405196</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4340808660384212</v>
+        <v>-0.4445412311265926</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2452563891981328</v>
+        <v>-0.259352608005841</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2907341226801066</v>
+        <v>-0.3031438458238966</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2851292054319856</v>
+        <v>-0.2991494233195198</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3813673685858703</v>
+        <v>-0.3951105882946209</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4028779679745753</v>
+        <v>-0.4181668950298416</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.473509150253463</v>
+        <v>-0.4647133127295575</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.45989269312863</v>
+        <v>-0.4765666176832895</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5644106478919326</v>
+        <v>-0.5824303104740238</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6129336849678779</v>
+        <v>-0.6069428487214452</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.602714433102328</v>
+        <v>-0.6238442207084134</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3961</v>
+        <v>3972</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.0400504039616365</v>
+        <v>-0.03834269063352735</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.09868569417176332</v>
+        <v>0.0984781582302503</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.00550392124344512</v>
+        <v>-0.005480325422574595</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2644801451728185</v>
+        <v>-0.2637224653799279</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.05866587755828334</v>
+        <v>-0.06116215634647659</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.07501412758046655</v>
+        <v>-0.07611904208992115</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.09558069910453071</v>
+        <v>-0.0979469113010154</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1455616964207991</v>
+        <v>-0.1478580237061706</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1674607008520752</v>
+        <v>-0.1710131228341254</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2720975641814505</v>
+        <v>-0.2767918910698413</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2356816320582098</v>
+        <v>-0.2405086644857377</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3385658406995233</v>
+        <v>-0.3444142652431665</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3912527866405497</v>
+        <v>-0.398328180741359</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4290214371166954</v>
+        <v>-0.4372733237675703</v>
       </c>
     </row>
     <row r="32">
@@ -5260,205 +5260,205 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4004</v>
+        <v>4015</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.02095103443951274</v>
+        <v>0.0221622565430053</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1409656054854835</v>
+        <v>0.1406321229842291</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.01613876364586986</v>
+        <v>-0.01608800118913223</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2709483149392469</v>
+        <v>-0.2701863354037357</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.09802787549823222</v>
+        <v>-0.0998711233432914</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.08609828503504247</v>
+        <v>-0.08690501270861972</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.05749239757889058</v>
+        <v>-0.05942417964005386</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.0620610957671488</v>
+        <v>-0.06403464746212961</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.05941459631699075</v>
+        <v>-0.062441072349813</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1720202912367981</v>
+        <v>-0.1758753692967545</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1880795169906477</v>
+        <v>-0.1919160106731752</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.189628257924042</v>
+        <v>-0.1944978117808489</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.2462233213268092</v>
+        <v>-0.252028155571459</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2311758593165578</v>
+        <v>-0.2380393334066468</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.208</t>
+          <t>X &lt; 0.2079</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4034</v>
+        <v>4045</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.002404947968237536</v>
+        <v>0.003441649731051655</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1095785486707257</v>
+        <v>0.1093238580123739</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.07401813134456603</v>
+        <v>-0.07381190821946859</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2270736862287492</v>
+        <v>-0.2264400211379325</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.05941973829092007</v>
+        <v>-0.0609948594662697</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.02062178035807705</v>
+        <v>-0.0214229115482425</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.01758728881804217</v>
+        <v>-0.01925763266715563</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.05033299028826832</v>
+        <v>-0.05195906623346502</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.02339759050973811</v>
+        <v>-0.02595682691033829</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.09194270495319756</v>
+        <v>-0.09525068035779327</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.08461307274047414</v>
+        <v>-0.08796186755829183</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.0363151156453867</v>
+        <v>-0.04064833624756403</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.04600890533194502</v>
+        <v>-0.05121253520567137</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.004555677317100049</v>
+        <v>-0.01070888070071874</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.2219</t>
+          <t>X &lt; 0.2218</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4059</v>
+        <v>4070</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.02512035273473856</v>
+        <v>-0.02419460715492505</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.02236606603582203</v>
+        <v>0.02234068329376271</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.06426908574879775</v>
+        <v>-0.06409134334651156</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1664296378049173</v>
+        <v>-0.1659663865546293</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.003099176464296249</v>
+        <v>-0.004518990004569901</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.06189025487756084</v>
+        <v>0.06101833681046287</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.009377051229954247</v>
+        <v>-0.01076489864603047</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.02019159976546092</v>
+        <v>-0.02158698737336806</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.006210385269717733</v>
+        <v>0.004036356457071122</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.04252294824127745</v>
+        <v>-0.04533441770732338</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.08572294429174576</v>
+        <v>-0.08843495311448635</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.03751095247370273</v>
+        <v>-0.04105490484261054</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.0004713979305677185</v>
+        <v>-0.004853014328517702</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.04212807252395834</v>
+        <v>0.03694299637020038</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.2358</t>
+          <t>X &lt; 0.2357</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4075</v>
+        <v>4086</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.03473207750108998</v>
+        <v>-0.03389811422584899</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.03072635694989856</v>
+        <v>0.03067399869313192</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1060609777609471</v>
+        <v>-0.1057723218381383</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1338821468945994</v>
+        <v>-0.1335100446428612</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.02670752778097807</v>
+        <v>0.02540287370009509</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1171066971284418</v>
+        <v>0.1161834572165787</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.07029802100420568</v>
+        <v>0.06888915395165895</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.08221800065987139</v>
+        <v>0.0807453358269683</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.05928279533610947</v>
+        <v>0.05726107688932558</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.03193561161795344</v>
+        <v>0.02932353006331567</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.01187977433823306</v>
+        <v>-0.01438888615731315</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.01176820024618763</v>
+        <v>0.008589653575540979</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.09609289527681852</v>
+        <v>0.09205063082442422</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1148952474907432</v>
+        <v>0.1102080916617254</v>
       </c>
     </row>
   </sheetData>
